--- a/HES_Budget_2026-2029.xlsx
+++ b/HES_Budget_2026-2029.xlsx
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,6 +171,8 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -558,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -578,6 +581,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -611,6 +615,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -644,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -677,6 +683,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -710,6 +717,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -730,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -763,6 +772,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
@@ -796,6 +806,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -868,6 +879,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -983,6 +995,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2052,6 +2065,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2097,11 +2111,11 @@
       </c>
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>IF(C6="";"";C6*D6)</f>
+        <f>IF(C6="","",C6*D6)</f>
         <v/>
       </c>
     </row>
@@ -2116,11 +2130,11 @@
       </c>
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>IF(C7="";"";C7*D7)</f>
+        <f>IF(C7="","",C7*D7)</f>
         <v/>
       </c>
     </row>
@@ -2135,11 +2149,11 @@
       </c>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>IF(C8="";"";C8*D8)</f>
+        <f>IF(C8="","",C8*D8)</f>
         <v/>
       </c>
     </row>
@@ -2154,11 +2168,11 @@
       </c>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>IF(C9="";"";C9*D9)</f>
+        <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
     </row>
@@ -2173,11 +2187,11 @@
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>IF(C10="";"";C10*D10)</f>
+        <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
     </row>
@@ -2192,11 +2206,11 @@
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>IF(C11="";"";C11*D11)</f>
+        <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
     </row>
@@ -2211,11 +2225,11 @@
       </c>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>IF(C12="";"";C12*D12)</f>
+        <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
     </row>
@@ -2230,11 +2244,11 @@
       </c>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>IF(C13="";"";C13*D13)</f>
+        <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
     </row>
@@ -2249,11 +2263,11 @@
       </c>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E14" s="12">
-        <f>IF(C14="";"";C14*D14)</f>
+        <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
     </row>
@@ -2268,11 +2282,11 @@
       </c>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>IF(C15="";"";C15*D15)</f>
+        <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
     </row>
@@ -2287,11 +2301,11 @@
       </c>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>IF(C16="";"";C16*D16)</f>
+        <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
     </row>
@@ -2306,11 +2320,11 @@
       </c>
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IF(C17="";"";C17*D17)</f>
+        <f>IF(C17="","",C17*D17)</f>
         <v/>
       </c>
     </row>
@@ -2325,11 +2339,11 @@
       </c>
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IF(C18="";"";C18*D18)</f>
+        <f>IF(C18="","",C18*D18)</f>
         <v/>
       </c>
     </row>
@@ -2344,11 +2358,11 @@
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>IF(C19="";"";C19*D19)</f>
+        <f>IF(C19="","",C19*D19)</f>
         <v/>
       </c>
     </row>
@@ -2363,11 +2377,11 @@
       </c>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>IF(C20="";"";C20*D20)</f>
+        <f>IF(C20="","",C20*D20)</f>
         <v/>
       </c>
     </row>
@@ -2382,11 +2396,11 @@
       </c>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>IF(C21="";"";C21*D21)</f>
+        <f>IF(C21="","",C21*D21)</f>
         <v/>
       </c>
     </row>
@@ -2401,11 +2415,11 @@
       </c>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>IF(C22="";"";C22*D22)</f>
+        <f>IF(C22="","",C22*D22)</f>
         <v/>
       </c>
     </row>
@@ -2420,11 +2434,11 @@
       </c>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>IF(C23="";"";C23*D23)</f>
+        <f>IF(C23="","",C23*D23)</f>
         <v/>
       </c>
     </row>
@@ -2439,11 +2453,11 @@
       </c>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>IF(C24="";"";C24*D24)</f>
+        <f>IF(C24="","",C24*D24)</f>
         <v/>
       </c>
     </row>
@@ -2458,11 +2472,11 @@
       </c>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>IF(C25="";"";C25*D25)</f>
+        <f>IF(C25="","",C25*D25)</f>
         <v/>
       </c>
     </row>
@@ -2477,11 +2491,11 @@
       </c>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>IF(C26="";"";C26*D26)</f>
+        <f>IF(C26="","",C26*D26)</f>
         <v/>
       </c>
     </row>
@@ -2496,11 +2510,11 @@
       </c>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>IF(C27="";"";C27*D27)</f>
+        <f>IF(C27="","",C27*D27)</f>
         <v/>
       </c>
     </row>
@@ -2515,11 +2529,11 @@
       </c>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>IF(C28="";"";C28*D28)</f>
+        <f>IF(C28="","",C28*D28)</f>
         <v/>
       </c>
     </row>
@@ -2534,11 +2548,11 @@
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>IF(C29="";"";C29*D29)</f>
+        <f>IF(C29="","",C29*D29)</f>
         <v/>
       </c>
     </row>
@@ -2553,11 +2567,11 @@
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>IF(C30="";"";C30*D30)</f>
+        <f>IF(C30="","",C30*D30)</f>
         <v/>
       </c>
     </row>
@@ -2572,11 +2586,11 @@
       </c>
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E31" s="12">
-        <f>IF(C31="";"";C31*D31)</f>
+        <f>IF(C31="","",C31*D31)</f>
         <v/>
       </c>
     </row>
@@ -2591,11 +2605,11 @@
       </c>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>IF(C32="";"";C32*D32)</f>
+        <f>IF(C32="","",C32*D32)</f>
         <v/>
       </c>
     </row>
@@ -2610,11 +2624,11 @@
       </c>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E33" s="12">
-        <f>IF(C33="";"";C33*D33)</f>
+        <f>IF(C33="","",C33*D33)</f>
         <v/>
       </c>
     </row>
@@ -2629,11 +2643,11 @@
       </c>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E34" s="12">
-        <f>IF(C34="";"";C34*D34)</f>
+        <f>IF(C34="","",C34*D34)</f>
         <v/>
       </c>
     </row>
@@ -2648,11 +2662,11 @@
       </c>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E35" s="12">
-        <f>IF(C35="";"";C35*D35)</f>
+        <f>IF(C35="","",C35*D35)</f>
         <v/>
       </c>
     </row>
@@ -2667,11 +2681,11 @@
       </c>
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E36" s="12">
-        <f>IF(C36="";"";C36*D36)</f>
+        <f>IF(C36="","",C36*D36)</f>
         <v/>
       </c>
     </row>
@@ -2686,11 +2700,11 @@
       </c>
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E37" s="12">
-        <f>IF(C37="";"";C37*D37)</f>
+        <f>IF(C37="","",C37*D37)</f>
         <v/>
       </c>
     </row>
@@ -2705,11 +2719,11 @@
       </c>
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E38" s="12">
-        <f>IF(C38="";"";C38*D38)</f>
+        <f>IF(C38="","",C38*D38)</f>
         <v/>
       </c>
     </row>
@@ -2724,11 +2738,11 @@
       </c>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E39" s="12">
-        <f>IF(C39="";"";C39*D39)</f>
+        <f>IF(C39="","",C39*D39)</f>
         <v/>
       </c>
     </row>
@@ -2743,11 +2757,11 @@
       </c>
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E40" s="12">
-        <f>IF(C40="";"";C40*D40)</f>
+        <f>IF(C40="","",C40*D40)</f>
         <v/>
       </c>
     </row>
@@ -2762,11 +2776,11 @@
       </c>
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="12">
-        <f>Aannames!B11</f>
+        <f>Aannames!B8</f>
         <v/>
       </c>
       <c r="E41" s="12">
-        <f>IF(C41="";"";C41*D41)</f>
+        <f>IF(C41="","",C41*D41)</f>
         <v/>
       </c>
     </row>
@@ -2787,6 +2801,7 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -2832,11 +2847,11 @@
       </c>
       <c r="C46" s="11" t="n"/>
       <c r="D46" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E46" s="12">
-        <f>IF(C46="";"";C46*D46)</f>
+        <f>IF(C46="","",C46*D46)</f>
         <v/>
       </c>
     </row>
@@ -2851,11 +2866,11 @@
       </c>
       <c r="C47" s="11" t="n"/>
       <c r="D47" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E47" s="12">
-        <f>IF(C47="";"";C47*D47)</f>
+        <f>IF(C47="","",C47*D47)</f>
         <v/>
       </c>
     </row>
@@ -2870,11 +2885,11 @@
       </c>
       <c r="C48" s="11" t="n"/>
       <c r="D48" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E48" s="12">
-        <f>IF(C48="";"";C48*D48)</f>
+        <f>IF(C48="","",C48*D48)</f>
         <v/>
       </c>
     </row>
@@ -2889,11 +2904,11 @@
       </c>
       <c r="C49" s="11" t="n"/>
       <c r="D49" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E49" s="12">
-        <f>IF(C49="";"";C49*D49)</f>
+        <f>IF(C49="","",C49*D49)</f>
         <v/>
       </c>
     </row>
@@ -2908,11 +2923,11 @@
       </c>
       <c r="C50" s="11" t="n"/>
       <c r="D50" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E50" s="12">
-        <f>IF(C50="";"";C50*D50)</f>
+        <f>IF(C50="","",C50*D50)</f>
         <v/>
       </c>
     </row>
@@ -2927,11 +2942,11 @@
       </c>
       <c r="C51" s="11" t="n"/>
       <c r="D51" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E51" s="12">
-        <f>IF(C51="";"";C51*D51)</f>
+        <f>IF(C51="","",C51*D51)</f>
         <v/>
       </c>
     </row>
@@ -2946,11 +2961,11 @@
       </c>
       <c r="C52" s="11" t="n"/>
       <c r="D52" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E52" s="12">
-        <f>IF(C52="";"";C52*D52)</f>
+        <f>IF(C52="","",C52*D52)</f>
         <v/>
       </c>
     </row>
@@ -2965,11 +2980,11 @@
       </c>
       <c r="C53" s="11" t="n"/>
       <c r="D53" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E53" s="12">
-        <f>IF(C53="";"";C53*D53)</f>
+        <f>IF(C53="","",C53*D53)</f>
         <v/>
       </c>
     </row>
@@ -2984,11 +2999,11 @@
       </c>
       <c r="C54" s="11" t="n"/>
       <c r="D54" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E54" s="12">
-        <f>IF(C54="";"";C54*D54)</f>
+        <f>IF(C54="","",C54*D54)</f>
         <v/>
       </c>
     </row>
@@ -3003,11 +3018,11 @@
       </c>
       <c r="C55" s="11" t="n"/>
       <c r="D55" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E55" s="12">
-        <f>IF(C55="";"";C55*D55)</f>
+        <f>IF(C55="","",C55*D55)</f>
         <v/>
       </c>
     </row>
@@ -3022,11 +3037,11 @@
       </c>
       <c r="C56" s="11" t="n"/>
       <c r="D56" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E56" s="12">
-        <f>IF(C56="";"";C56*D56)</f>
+        <f>IF(C56="","",C56*D56)</f>
         <v/>
       </c>
     </row>
@@ -3041,11 +3056,11 @@
       </c>
       <c r="C57" s="11" t="n"/>
       <c r="D57" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E57" s="12">
-        <f>IF(C57="";"";C57*D57)</f>
+        <f>IF(C57="","",C57*D57)</f>
         <v/>
       </c>
     </row>
@@ -3060,11 +3075,11 @@
       </c>
       <c r="C58" s="11" t="n"/>
       <c r="D58" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E58" s="12">
-        <f>IF(C58="";"";C58*D58)</f>
+        <f>IF(C58="","",C58*D58)</f>
         <v/>
       </c>
     </row>
@@ -3079,11 +3094,11 @@
       </c>
       <c r="C59" s="11" t="n"/>
       <c r="D59" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E59" s="12">
-        <f>IF(C59="";"";C59*D59)</f>
+        <f>IF(C59="","",C59*D59)</f>
         <v/>
       </c>
     </row>
@@ -3098,11 +3113,11 @@
       </c>
       <c r="C60" s="11" t="n"/>
       <c r="D60" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E60" s="12">
-        <f>IF(C60="";"";C60*D60)</f>
+        <f>IF(C60="","",C60*D60)</f>
         <v/>
       </c>
     </row>
@@ -3117,11 +3132,11 @@
       </c>
       <c r="C61" s="11" t="n"/>
       <c r="D61" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E61" s="12">
-        <f>IF(C61="";"";C61*D61)</f>
+        <f>IF(C61="","",C61*D61)</f>
         <v/>
       </c>
     </row>
@@ -3136,11 +3151,11 @@
       </c>
       <c r="C62" s="11" t="n"/>
       <c r="D62" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E62" s="12">
-        <f>IF(C62="";"";C62*D62)</f>
+        <f>IF(C62="","",C62*D62)</f>
         <v/>
       </c>
     </row>
@@ -3155,11 +3170,11 @@
       </c>
       <c r="C63" s="11" t="n"/>
       <c r="D63" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E63" s="12">
-        <f>IF(C63="";"";C63*D63)</f>
+        <f>IF(C63="","",C63*D63)</f>
         <v/>
       </c>
     </row>
@@ -3174,11 +3189,11 @@
       </c>
       <c r="C64" s="11" t="n"/>
       <c r="D64" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E64" s="12">
-        <f>IF(C64="";"";C64*D64)</f>
+        <f>IF(C64="","",C64*D64)</f>
         <v/>
       </c>
     </row>
@@ -3193,11 +3208,11 @@
       </c>
       <c r="C65" s="11" t="n"/>
       <c r="D65" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E65" s="12">
-        <f>IF(C65="";"";C65*D65)</f>
+        <f>IF(C65="","",C65*D65)</f>
         <v/>
       </c>
     </row>
@@ -3212,11 +3227,11 @@
       </c>
       <c r="C66" s="11" t="n"/>
       <c r="D66" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E66" s="12">
-        <f>IF(C66="";"";C66*D66)</f>
+        <f>IF(C66="","",C66*D66)</f>
         <v/>
       </c>
     </row>
@@ -3231,11 +3246,11 @@
       </c>
       <c r="C67" s="11" t="n"/>
       <c r="D67" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E67" s="12">
-        <f>IF(C67="";"";C67*D67)</f>
+        <f>IF(C67="","",C67*D67)</f>
         <v/>
       </c>
     </row>
@@ -3250,11 +3265,11 @@
       </c>
       <c r="C68" s="11" t="n"/>
       <c r="D68" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E68" s="12">
-        <f>IF(C68="";"";C68*D68)</f>
+        <f>IF(C68="","",C68*D68)</f>
         <v/>
       </c>
     </row>
@@ -3269,11 +3284,11 @@
       </c>
       <c r="C69" s="11" t="n"/>
       <c r="D69" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E69" s="12">
-        <f>IF(C69="";"";C69*D69)</f>
+        <f>IF(C69="","",C69*D69)</f>
         <v/>
       </c>
     </row>
@@ -3288,11 +3303,11 @@
       </c>
       <c r="C70" s="11" t="n"/>
       <c r="D70" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E70" s="12">
-        <f>IF(C70="";"";C70*D70)</f>
+        <f>IF(C70="","",C70*D70)</f>
         <v/>
       </c>
     </row>
@@ -3307,11 +3322,11 @@
       </c>
       <c r="C71" s="11" t="n"/>
       <c r="D71" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E71" s="12">
-        <f>IF(C71="";"";C71*D71)</f>
+        <f>IF(C71="","",C71*D71)</f>
         <v/>
       </c>
     </row>
@@ -3326,11 +3341,11 @@
       </c>
       <c r="C72" s="11" t="n"/>
       <c r="D72" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E72" s="12">
-        <f>IF(C72="";"";C72*D72)</f>
+        <f>IF(C72="","",C72*D72)</f>
         <v/>
       </c>
     </row>
@@ -3345,11 +3360,11 @@
       </c>
       <c r="C73" s="11" t="n"/>
       <c r="D73" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E73" s="12">
-        <f>IF(C73="";"";C73*D73)</f>
+        <f>IF(C73="","",C73*D73)</f>
         <v/>
       </c>
     </row>
@@ -3364,11 +3379,11 @@
       </c>
       <c r="C74" s="11" t="n"/>
       <c r="D74" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E74" s="12">
-        <f>IF(C74="";"";C74*D74)</f>
+        <f>IF(C74="","",C74*D74)</f>
         <v/>
       </c>
     </row>
@@ -3383,11 +3398,11 @@
       </c>
       <c r="C75" s="11" t="n"/>
       <c r="D75" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E75" s="12">
-        <f>IF(C75="";"";C75*D75)</f>
+        <f>IF(C75="","",C75*D75)</f>
         <v/>
       </c>
     </row>
@@ -3402,11 +3417,11 @@
       </c>
       <c r="C76" s="11" t="n"/>
       <c r="D76" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E76" s="12">
-        <f>IF(C76="";"";C76*D76)</f>
+        <f>IF(C76="","",C76*D76)</f>
         <v/>
       </c>
     </row>
@@ -3421,11 +3436,11 @@
       </c>
       <c r="C77" s="11" t="n"/>
       <c r="D77" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E77" s="12">
-        <f>IF(C77="";"";C77*D77)</f>
+        <f>IF(C77="","",C77*D77)</f>
         <v/>
       </c>
     </row>
@@ -3440,11 +3455,11 @@
       </c>
       <c r="C78" s="11" t="n"/>
       <c r="D78" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E78" s="12">
-        <f>IF(C78="";"";C78*D78)</f>
+        <f>IF(C78="","",C78*D78)</f>
         <v/>
       </c>
     </row>
@@ -3459,11 +3474,11 @@
       </c>
       <c r="C79" s="11" t="n"/>
       <c r="D79" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E79" s="12">
-        <f>IF(C79="";"";C79*D79)</f>
+        <f>IF(C79="","",C79*D79)</f>
         <v/>
       </c>
     </row>
@@ -3478,11 +3493,11 @@
       </c>
       <c r="C80" s="11" t="n"/>
       <c r="D80" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E80" s="12">
-        <f>IF(C80="";"";C80*D80)</f>
+        <f>IF(C80="","",C80*D80)</f>
         <v/>
       </c>
     </row>
@@ -3497,11 +3512,11 @@
       </c>
       <c r="C81" s="11" t="n"/>
       <c r="D81" s="12">
-        <f>Aannames!B15</f>
+        <f>Aannames!B12</f>
         <v/>
       </c>
       <c r="E81" s="12">
-        <f>IF(C81="";"";C81*D81)</f>
+        <f>IF(C81="","",C81*D81)</f>
         <v/>
       </c>
     </row>
@@ -3522,6 +3537,7 @@
         <v/>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
@@ -3567,11 +3583,11 @@
       </c>
       <c r="C86" s="11" t="n"/>
       <c r="D86" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E86" s="12">
-        <f>IF(C86="";"";C86*D86)</f>
+        <f>IF(C86="","",C86*D86)</f>
         <v/>
       </c>
     </row>
@@ -3586,11 +3602,11 @@
       </c>
       <c r="C87" s="11" t="n"/>
       <c r="D87" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E87" s="12">
-        <f>IF(C87="";"";C87*D87)</f>
+        <f>IF(C87="","",C87*D87)</f>
         <v/>
       </c>
     </row>
@@ -3605,11 +3621,11 @@
       </c>
       <c r="C88" s="11" t="n"/>
       <c r="D88" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E88" s="12">
-        <f>IF(C88="";"";C88*D88)</f>
+        <f>IF(C88="","",C88*D88)</f>
         <v/>
       </c>
     </row>
@@ -3624,11 +3640,11 @@
       </c>
       <c r="C89" s="11" t="n"/>
       <c r="D89" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E89" s="12">
-        <f>IF(C89="";"";C89*D89)</f>
+        <f>IF(C89="","",C89*D89)</f>
         <v/>
       </c>
     </row>
@@ -3643,11 +3659,11 @@
       </c>
       <c r="C90" s="11" t="n"/>
       <c r="D90" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E90" s="12">
-        <f>IF(C90="";"";C90*D90)</f>
+        <f>IF(C90="","",C90*D90)</f>
         <v/>
       </c>
     </row>
@@ -3662,11 +3678,11 @@
       </c>
       <c r="C91" s="11" t="n"/>
       <c r="D91" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E91" s="12">
-        <f>IF(C91="";"";C91*D91)</f>
+        <f>IF(C91="","",C91*D91)</f>
         <v/>
       </c>
     </row>
@@ -3681,11 +3697,11 @@
       </c>
       <c r="C92" s="11" t="n"/>
       <c r="D92" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E92" s="12">
-        <f>IF(C92="";"";C92*D92)</f>
+        <f>IF(C92="","",C92*D92)</f>
         <v/>
       </c>
     </row>
@@ -3700,11 +3716,11 @@
       </c>
       <c r="C93" s="11" t="n"/>
       <c r="D93" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E93" s="12">
-        <f>IF(C93="";"";C93*D93)</f>
+        <f>IF(C93="","",C93*D93)</f>
         <v/>
       </c>
     </row>
@@ -3719,11 +3735,11 @@
       </c>
       <c r="C94" s="11" t="n"/>
       <c r="D94" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E94" s="12">
-        <f>IF(C94="";"";C94*D94)</f>
+        <f>IF(C94="","",C94*D94)</f>
         <v/>
       </c>
     </row>
@@ -3738,11 +3754,11 @@
       </c>
       <c r="C95" s="11" t="n"/>
       <c r="D95" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E95" s="12">
-        <f>IF(C95="";"";C95*D95)</f>
+        <f>IF(C95="","",C95*D95)</f>
         <v/>
       </c>
     </row>
@@ -3757,11 +3773,11 @@
       </c>
       <c r="C96" s="11" t="n"/>
       <c r="D96" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E96" s="12">
-        <f>IF(C96="";"";C96*D96)</f>
+        <f>IF(C96="","",C96*D96)</f>
         <v/>
       </c>
     </row>
@@ -3776,11 +3792,11 @@
       </c>
       <c r="C97" s="11" t="n"/>
       <c r="D97" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E97" s="12">
-        <f>IF(C97="";"";C97*D97)</f>
+        <f>IF(C97="","",C97*D97)</f>
         <v/>
       </c>
     </row>
@@ -3795,11 +3811,11 @@
       </c>
       <c r="C98" s="11" t="n"/>
       <c r="D98" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E98" s="12">
-        <f>IF(C98="";"";C98*D98)</f>
+        <f>IF(C98="","",C98*D98)</f>
         <v/>
       </c>
     </row>
@@ -3814,11 +3830,11 @@
       </c>
       <c r="C99" s="11" t="n"/>
       <c r="D99" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E99" s="12">
-        <f>IF(C99="";"";C99*D99)</f>
+        <f>IF(C99="","",C99*D99)</f>
         <v/>
       </c>
     </row>
@@ -3833,11 +3849,11 @@
       </c>
       <c r="C100" s="11" t="n"/>
       <c r="D100" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E100" s="12">
-        <f>IF(C100="";"";C100*D100)</f>
+        <f>IF(C100="","",C100*D100)</f>
         <v/>
       </c>
     </row>
@@ -3852,11 +3868,11 @@
       </c>
       <c r="C101" s="11" t="n"/>
       <c r="D101" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E101" s="12">
-        <f>IF(C101="";"";C101*D101)</f>
+        <f>IF(C101="","",C101*D101)</f>
         <v/>
       </c>
     </row>
@@ -3871,11 +3887,11 @@
       </c>
       <c r="C102" s="11" t="n"/>
       <c r="D102" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E102" s="12">
-        <f>IF(C102="";"";C102*D102)</f>
+        <f>IF(C102="","",C102*D102)</f>
         <v/>
       </c>
     </row>
@@ -3890,11 +3906,11 @@
       </c>
       <c r="C103" s="11" t="n"/>
       <c r="D103" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E103" s="12">
-        <f>IF(C103="";"";C103*D103)</f>
+        <f>IF(C103="","",C103*D103)</f>
         <v/>
       </c>
     </row>
@@ -3909,11 +3925,11 @@
       </c>
       <c r="C104" s="11" t="n"/>
       <c r="D104" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E104" s="12">
-        <f>IF(C104="";"";C104*D104)</f>
+        <f>IF(C104="","",C104*D104)</f>
         <v/>
       </c>
     </row>
@@ -3928,11 +3944,11 @@
       </c>
       <c r="C105" s="11" t="n"/>
       <c r="D105" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E105" s="12">
-        <f>IF(C105="";"";C105*D105)</f>
+        <f>IF(C105="","",C105*D105)</f>
         <v/>
       </c>
     </row>
@@ -3947,11 +3963,11 @@
       </c>
       <c r="C106" s="11" t="n"/>
       <c r="D106" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E106" s="12">
-        <f>IF(C106="";"";C106*D106)</f>
+        <f>IF(C106="","",C106*D106)</f>
         <v/>
       </c>
     </row>
@@ -3966,11 +3982,11 @@
       </c>
       <c r="C107" s="11" t="n"/>
       <c r="D107" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E107" s="12">
-        <f>IF(C107="";"";C107*D107)</f>
+        <f>IF(C107="","",C107*D107)</f>
         <v/>
       </c>
     </row>
@@ -3985,11 +4001,11 @@
       </c>
       <c r="C108" s="11" t="n"/>
       <c r="D108" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E108" s="12">
-        <f>IF(C108="";"";C108*D108)</f>
+        <f>IF(C108="","",C108*D108)</f>
         <v/>
       </c>
     </row>
@@ -4004,11 +4020,11 @@
       </c>
       <c r="C109" s="11" t="n"/>
       <c r="D109" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E109" s="12">
-        <f>IF(C109="";"";C109*D109)</f>
+        <f>IF(C109="","",C109*D109)</f>
         <v/>
       </c>
     </row>
@@ -4023,11 +4039,11 @@
       </c>
       <c r="C110" s="11" t="n"/>
       <c r="D110" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E110" s="12">
-        <f>IF(C110="";"";C110*D110)</f>
+        <f>IF(C110="","",C110*D110)</f>
         <v/>
       </c>
     </row>
@@ -4042,11 +4058,11 @@
       </c>
       <c r="C111" s="11" t="n"/>
       <c r="D111" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E111" s="12">
-        <f>IF(C111="";"";C111*D111)</f>
+        <f>IF(C111="","",C111*D111)</f>
         <v/>
       </c>
     </row>
@@ -4061,11 +4077,11 @@
       </c>
       <c r="C112" s="11" t="n"/>
       <c r="D112" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E112" s="12">
-        <f>IF(C112="";"";C112*D112)</f>
+        <f>IF(C112="","",C112*D112)</f>
         <v/>
       </c>
     </row>
@@ -4080,11 +4096,11 @@
       </c>
       <c r="C113" s="11" t="n"/>
       <c r="D113" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E113" s="12">
-        <f>IF(C113="";"";C113*D113)</f>
+        <f>IF(C113="","",C113*D113)</f>
         <v/>
       </c>
     </row>
@@ -4099,11 +4115,11 @@
       </c>
       <c r="C114" s="11" t="n"/>
       <c r="D114" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E114" s="12">
-        <f>IF(C114="";"";C114*D114)</f>
+        <f>IF(C114="","",C114*D114)</f>
         <v/>
       </c>
     </row>
@@ -4118,11 +4134,11 @@
       </c>
       <c r="C115" s="11" t="n"/>
       <c r="D115" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E115" s="12">
-        <f>IF(C115="";"";C115*D115)</f>
+        <f>IF(C115="","",C115*D115)</f>
         <v/>
       </c>
     </row>
@@ -4137,11 +4153,11 @@
       </c>
       <c r="C116" s="11" t="n"/>
       <c r="D116" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E116" s="12">
-        <f>IF(C116="";"";C116*D116)</f>
+        <f>IF(C116="","",C116*D116)</f>
         <v/>
       </c>
     </row>
@@ -4156,11 +4172,11 @@
       </c>
       <c r="C117" s="11" t="n"/>
       <c r="D117" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E117" s="12">
-        <f>IF(C117="";"";C117*D117)</f>
+        <f>IF(C117="","",C117*D117)</f>
         <v/>
       </c>
     </row>
@@ -4175,11 +4191,11 @@
       </c>
       <c r="C118" s="11" t="n"/>
       <c r="D118" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E118" s="12">
-        <f>IF(C118="";"";C118*D118)</f>
+        <f>IF(C118="","",C118*D118)</f>
         <v/>
       </c>
     </row>
@@ -4194,11 +4210,11 @@
       </c>
       <c r="C119" s="11" t="n"/>
       <c r="D119" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E119" s="12">
-        <f>IF(C119="";"";C119*D119)</f>
+        <f>IF(C119="","",C119*D119)</f>
         <v/>
       </c>
     </row>
@@ -4213,11 +4229,11 @@
       </c>
       <c r="C120" s="11" t="n"/>
       <c r="D120" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E120" s="12">
-        <f>IF(C120="";"";C120*D120)</f>
+        <f>IF(C120="","",C120*D120)</f>
         <v/>
       </c>
     </row>
@@ -4232,11 +4248,11 @@
       </c>
       <c r="C121" s="11" t="n"/>
       <c r="D121" s="12">
-        <f>Aannames!B19</f>
+        <f>Aannames!B16</f>
         <v/>
       </c>
       <c r="E121" s="12">
-        <f>IF(C121="";"";C121*D121)</f>
+        <f>IF(C121="","",C121*D121)</f>
         <v/>
       </c>
     </row>
@@ -4257,6 +4273,7 @@
         <v/>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
@@ -4302,11 +4319,11 @@
       </c>
       <c r="C126" s="11" t="n"/>
       <c r="D126" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E126" s="12">
-        <f>IF(C126="";"";C126*D126)</f>
+        <f>IF(C126="","",C126*D126)</f>
         <v/>
       </c>
     </row>
@@ -4321,11 +4338,11 @@
       </c>
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E127" s="12">
-        <f>IF(C127="";"";C127*D127)</f>
+        <f>IF(C127="","",C127*D127)</f>
         <v/>
       </c>
     </row>
@@ -4340,11 +4357,11 @@
       </c>
       <c r="C128" s="11" t="n"/>
       <c r="D128" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E128" s="12">
-        <f>IF(C128="";"";C128*D128)</f>
+        <f>IF(C128="","",C128*D128)</f>
         <v/>
       </c>
     </row>
@@ -4359,11 +4376,11 @@
       </c>
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E129" s="12">
-        <f>IF(C129="";"";C129*D129)</f>
+        <f>IF(C129="","",C129*D129)</f>
         <v/>
       </c>
     </row>
@@ -4378,11 +4395,11 @@
       </c>
       <c r="C130" s="11" t="n"/>
       <c r="D130" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E130" s="12">
-        <f>IF(C130="";"";C130*D130)</f>
+        <f>IF(C130="","",C130*D130)</f>
         <v/>
       </c>
     </row>
@@ -4397,11 +4414,11 @@
       </c>
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E131" s="12">
-        <f>IF(C131="";"";C131*D131)</f>
+        <f>IF(C131="","",C131*D131)</f>
         <v/>
       </c>
     </row>
@@ -4416,11 +4433,11 @@
       </c>
       <c r="C132" s="11" t="n"/>
       <c r="D132" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E132" s="12">
-        <f>IF(C132="";"";C132*D132)</f>
+        <f>IF(C132="","",C132*D132)</f>
         <v/>
       </c>
     </row>
@@ -4435,11 +4452,11 @@
       </c>
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E133" s="12">
-        <f>IF(C133="";"";C133*D133)</f>
+        <f>IF(C133="","",C133*D133)</f>
         <v/>
       </c>
     </row>
@@ -4454,11 +4471,11 @@
       </c>
       <c r="C134" s="11" t="n"/>
       <c r="D134" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E134" s="12">
-        <f>IF(C134="";"";C134*D134)</f>
+        <f>IF(C134="","",C134*D134)</f>
         <v/>
       </c>
     </row>
@@ -4473,11 +4490,11 @@
       </c>
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E135" s="12">
-        <f>IF(C135="";"";C135*D135)</f>
+        <f>IF(C135="","",C135*D135)</f>
         <v/>
       </c>
     </row>
@@ -4492,11 +4509,11 @@
       </c>
       <c r="C136" s="11" t="n"/>
       <c r="D136" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E136" s="12">
-        <f>IF(C136="";"";C136*D136)</f>
+        <f>IF(C136="","",C136*D136)</f>
         <v/>
       </c>
     </row>
@@ -4511,11 +4528,11 @@
       </c>
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E137" s="12">
-        <f>IF(C137="";"";C137*D137)</f>
+        <f>IF(C137="","",C137*D137)</f>
         <v/>
       </c>
     </row>
@@ -4530,11 +4547,11 @@
       </c>
       <c r="C138" s="11" t="n"/>
       <c r="D138" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E138" s="12">
-        <f>IF(C138="";"";C138*D138)</f>
+        <f>IF(C138="","",C138*D138)</f>
         <v/>
       </c>
     </row>
@@ -4549,11 +4566,11 @@
       </c>
       <c r="C139" s="11" t="n"/>
       <c r="D139" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E139" s="12">
-        <f>IF(C139="";"";C139*D139)</f>
+        <f>IF(C139="","",C139*D139)</f>
         <v/>
       </c>
     </row>
@@ -4568,11 +4585,11 @@
       </c>
       <c r="C140" s="11" t="n"/>
       <c r="D140" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E140" s="12">
-        <f>IF(C140="";"";C140*D140)</f>
+        <f>IF(C140="","",C140*D140)</f>
         <v/>
       </c>
     </row>
@@ -4587,11 +4604,11 @@
       </c>
       <c r="C141" s="11" t="n"/>
       <c r="D141" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E141" s="12">
-        <f>IF(C141="";"";C141*D141)</f>
+        <f>IF(C141="","",C141*D141)</f>
         <v/>
       </c>
     </row>
@@ -4606,11 +4623,11 @@
       </c>
       <c r="C142" s="11" t="n"/>
       <c r="D142" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E142" s="12">
-        <f>IF(C142="";"";C142*D142)</f>
+        <f>IF(C142="","",C142*D142)</f>
         <v/>
       </c>
     </row>
@@ -4625,11 +4642,11 @@
       </c>
       <c r="C143" s="11" t="n"/>
       <c r="D143" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E143" s="12">
-        <f>IF(C143="";"";C143*D143)</f>
+        <f>IF(C143="","",C143*D143)</f>
         <v/>
       </c>
     </row>
@@ -4644,11 +4661,11 @@
       </c>
       <c r="C144" s="11" t="n"/>
       <c r="D144" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E144" s="12">
-        <f>IF(C144="";"";C144*D144)</f>
+        <f>IF(C144="","",C144*D144)</f>
         <v/>
       </c>
     </row>
@@ -4663,11 +4680,11 @@
       </c>
       <c r="C145" s="11" t="n"/>
       <c r="D145" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E145" s="12">
-        <f>IF(C145="";"";C145*D145)</f>
+        <f>IF(C145="","",C145*D145)</f>
         <v/>
       </c>
     </row>
@@ -4682,11 +4699,11 @@
       </c>
       <c r="C146" s="11" t="n"/>
       <c r="D146" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E146" s="12">
-        <f>IF(C146="";"";C146*D146)</f>
+        <f>IF(C146="","",C146*D146)</f>
         <v/>
       </c>
     </row>
@@ -4701,11 +4718,11 @@
       </c>
       <c r="C147" s="11" t="n"/>
       <c r="D147" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E147" s="12">
-        <f>IF(C147="";"";C147*D147)</f>
+        <f>IF(C147="","",C147*D147)</f>
         <v/>
       </c>
     </row>
@@ -4720,11 +4737,11 @@
       </c>
       <c r="C148" s="11" t="n"/>
       <c r="D148" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E148" s="12">
-        <f>IF(C148="";"";C148*D148)</f>
+        <f>IF(C148="","",C148*D148)</f>
         <v/>
       </c>
     </row>
@@ -4739,11 +4756,11 @@
       </c>
       <c r="C149" s="11" t="n"/>
       <c r="D149" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E149" s="12">
-        <f>IF(C149="";"";C149*D149)</f>
+        <f>IF(C149="","",C149*D149)</f>
         <v/>
       </c>
     </row>
@@ -4758,11 +4775,11 @@
       </c>
       <c r="C150" s="11" t="n"/>
       <c r="D150" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E150" s="12">
-        <f>IF(C150="";"";C150*D150)</f>
+        <f>IF(C150="","",C150*D150)</f>
         <v/>
       </c>
     </row>
@@ -4777,11 +4794,11 @@
       </c>
       <c r="C151" s="11" t="n"/>
       <c r="D151" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E151" s="12">
-        <f>IF(C151="";"";C151*D151)</f>
+        <f>IF(C151="","",C151*D151)</f>
         <v/>
       </c>
     </row>
@@ -4796,11 +4813,11 @@
       </c>
       <c r="C152" s="11" t="n"/>
       <c r="D152" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E152" s="12">
-        <f>IF(C152="";"";C152*D152)</f>
+        <f>IF(C152="","",C152*D152)</f>
         <v/>
       </c>
     </row>
@@ -4815,11 +4832,11 @@
       </c>
       <c r="C153" s="11" t="n"/>
       <c r="D153" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E153" s="12">
-        <f>IF(C153="";"";C153*D153)</f>
+        <f>IF(C153="","",C153*D153)</f>
         <v/>
       </c>
     </row>
@@ -4834,11 +4851,11 @@
       </c>
       <c r="C154" s="11" t="n"/>
       <c r="D154" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E154" s="12">
-        <f>IF(C154="";"";C154*D154)</f>
+        <f>IF(C154="","",C154*D154)</f>
         <v/>
       </c>
     </row>
@@ -4853,11 +4870,11 @@
       </c>
       <c r="C155" s="11" t="n"/>
       <c r="D155" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E155" s="12">
-        <f>IF(C155="";"";C155*D155)</f>
+        <f>IF(C155="","",C155*D155)</f>
         <v/>
       </c>
     </row>
@@ -4872,11 +4889,11 @@
       </c>
       <c r="C156" s="11" t="n"/>
       <c r="D156" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E156" s="12">
-        <f>IF(C156="";"";C156*D156)</f>
+        <f>IF(C156="","",C156*D156)</f>
         <v/>
       </c>
     </row>
@@ -4891,11 +4908,11 @@
       </c>
       <c r="C157" s="11" t="n"/>
       <c r="D157" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E157" s="12">
-        <f>IF(C157="";"";C157*D157)</f>
+        <f>IF(C157="","",C157*D157)</f>
         <v/>
       </c>
     </row>
@@ -4910,11 +4927,11 @@
       </c>
       <c r="C158" s="11" t="n"/>
       <c r="D158" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E158" s="12">
-        <f>IF(C158="";"";C158*D158)</f>
+        <f>IF(C158="","",C158*D158)</f>
         <v/>
       </c>
     </row>
@@ -4929,11 +4946,11 @@
       </c>
       <c r="C159" s="11" t="n"/>
       <c r="D159" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E159" s="12">
-        <f>IF(C159="";"";C159*D159)</f>
+        <f>IF(C159="","",C159*D159)</f>
         <v/>
       </c>
     </row>
@@ -4948,11 +4965,11 @@
       </c>
       <c r="C160" s="11" t="n"/>
       <c r="D160" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E160" s="12">
-        <f>IF(C160="";"";C160*D160)</f>
+        <f>IF(C160="","",C160*D160)</f>
         <v/>
       </c>
     </row>
@@ -4967,11 +4984,11 @@
       </c>
       <c r="C161" s="11" t="n"/>
       <c r="D161" s="12">
-        <f>Aannames!B27</f>
+        <f>Aannames!B24</f>
         <v/>
       </c>
       <c r="E161" s="12">
-        <f>IF(C161="";"";C161*D161)</f>
+        <f>IF(C161="","",C161*D161)</f>
         <v/>
       </c>
     </row>
@@ -4992,6 +5009,7 @@
         <v/>
       </c>
     </row>
+    <row r="163"/>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
@@ -5036,9 +5054,12 @@
         </is>
       </c>
       <c r="C166" s="11" t="n"/>
-      <c r="D166" s="11" t="n"/>
+      <c r="D166" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E166" s="12">
-        <f>IF(C166="";"";C166*D166)</f>
+        <f>IF(C166="","",C166*D166)</f>
         <v/>
       </c>
     </row>
@@ -5052,9 +5073,12 @@
         </is>
       </c>
       <c r="C167" s="11" t="n"/>
-      <c r="D167" s="11" t="n"/>
+      <c r="D167" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E167" s="12">
-        <f>IF(C167="";"";C167*D167)</f>
+        <f>IF(C167="","",C167*D167)</f>
         <v/>
       </c>
     </row>
@@ -5068,9 +5092,12 @@
         </is>
       </c>
       <c r="C168" s="11" t="n"/>
-      <c r="D168" s="11" t="n"/>
+      <c r="D168" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E168" s="12">
-        <f>IF(C168="";"";C168*D168)</f>
+        <f>IF(C168="","",C168*D168)</f>
         <v/>
       </c>
     </row>
@@ -5084,9 +5111,12 @@
         </is>
       </c>
       <c r="C169" s="11" t="n"/>
-      <c r="D169" s="11" t="n"/>
+      <c r="D169" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E169" s="12">
-        <f>IF(C169="";"";C169*D169)</f>
+        <f>IF(C169="","",C169*D169)</f>
         <v/>
       </c>
     </row>
@@ -5100,9 +5130,12 @@
         </is>
       </c>
       <c r="C170" s="11" t="n"/>
-      <c r="D170" s="11" t="n"/>
+      <c r="D170" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E170" s="12">
-        <f>IF(C170="";"";C170*D170)</f>
+        <f>IF(C170="","",C170*D170)</f>
         <v/>
       </c>
     </row>
@@ -5116,9 +5149,12 @@
         </is>
       </c>
       <c r="C171" s="11" t="n"/>
-      <c r="D171" s="11" t="n"/>
+      <c r="D171" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E171" s="12">
-        <f>IF(C171="";"";C171*D171)</f>
+        <f>IF(C171="","",C171*D171)</f>
         <v/>
       </c>
     </row>
@@ -5132,9 +5168,12 @@
         </is>
       </c>
       <c r="C172" s="11" t="n"/>
-      <c r="D172" s="11" t="n"/>
+      <c r="D172" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E172" s="12">
-        <f>IF(C172="";"";C172*D172)</f>
+        <f>IF(C172="","",C172*D172)</f>
         <v/>
       </c>
     </row>
@@ -5148,9 +5187,12 @@
         </is>
       </c>
       <c r="C173" s="11" t="n"/>
-      <c r="D173" s="11" t="n"/>
+      <c r="D173" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E173" s="12">
-        <f>IF(C173="";"";C173*D173)</f>
+        <f>IF(C173="","",C173*D173)</f>
         <v/>
       </c>
     </row>
@@ -5164,9 +5206,12 @@
         </is>
       </c>
       <c r="C174" s="11" t="n"/>
-      <c r="D174" s="11" t="n"/>
+      <c r="D174" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E174" s="12">
-        <f>IF(C174="";"";C174*D174)</f>
+        <f>IF(C174="","",C174*D174)</f>
         <v/>
       </c>
     </row>
@@ -5180,9 +5225,12 @@
         </is>
       </c>
       <c r="C175" s="11" t="n"/>
-      <c r="D175" s="11" t="n"/>
+      <c r="D175" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E175" s="12">
-        <f>IF(C175="";"";C175*D175)</f>
+        <f>IF(C175="","",C175*D175)</f>
         <v/>
       </c>
     </row>
@@ -5196,9 +5244,12 @@
         </is>
       </c>
       <c r="C176" s="11" t="n"/>
-      <c r="D176" s="11" t="n"/>
+      <c r="D176" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E176" s="12">
-        <f>IF(C176="";"";C176*D176)</f>
+        <f>IF(C176="","",C176*D176)</f>
         <v/>
       </c>
     </row>
@@ -5212,9 +5263,12 @@
         </is>
       </c>
       <c r="C177" s="11" t="n"/>
-      <c r="D177" s="11" t="n"/>
+      <c r="D177" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E177" s="12">
-        <f>IF(C177="";"";C177*D177)</f>
+        <f>IF(C177="","",C177*D177)</f>
         <v/>
       </c>
     </row>
@@ -5228,9 +5282,12 @@
         </is>
       </c>
       <c r="C178" s="11" t="n"/>
-      <c r="D178" s="11" t="n"/>
+      <c r="D178" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E178" s="12">
-        <f>IF(C178="";"";C178*D178)</f>
+        <f>IF(C178="","",C178*D178)</f>
         <v/>
       </c>
     </row>
@@ -5244,9 +5301,12 @@
         </is>
       </c>
       <c r="C179" s="11" t="n"/>
-      <c r="D179" s="11" t="n"/>
+      <c r="D179" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E179" s="12">
-        <f>IF(C179="";"";C179*D179)</f>
+        <f>IF(C179="","",C179*D179)</f>
         <v/>
       </c>
     </row>
@@ -5260,9 +5320,12 @@
         </is>
       </c>
       <c r="C180" s="11" t="n"/>
-      <c r="D180" s="11" t="n"/>
+      <c r="D180" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E180" s="12">
-        <f>IF(C180="";"";C180*D180)</f>
+        <f>IF(C180="","",C180*D180)</f>
         <v/>
       </c>
     </row>
@@ -5276,9 +5339,12 @@
         </is>
       </c>
       <c r="C181" s="11" t="n"/>
-      <c r="D181" s="11" t="n"/>
+      <c r="D181" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E181" s="12">
-        <f>IF(C181="";"";C181*D181)</f>
+        <f>IF(C181="","",C181*D181)</f>
         <v/>
       </c>
     </row>
@@ -5292,9 +5358,12 @@
         </is>
       </c>
       <c r="C182" s="11" t="n"/>
-      <c r="D182" s="11" t="n"/>
+      <c r="D182" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E182" s="12">
-        <f>IF(C182="";"";C182*D182)</f>
+        <f>IF(C182="","",C182*D182)</f>
         <v/>
       </c>
     </row>
@@ -5308,9 +5377,12 @@
         </is>
       </c>
       <c r="C183" s="11" t="n"/>
-      <c r="D183" s="11" t="n"/>
+      <c r="D183" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E183" s="12">
-        <f>IF(C183="";"";C183*D183)</f>
+        <f>IF(C183="","",C183*D183)</f>
         <v/>
       </c>
     </row>
@@ -5324,9 +5396,12 @@
         </is>
       </c>
       <c r="C184" s="11" t="n"/>
-      <c r="D184" s="11" t="n"/>
+      <c r="D184" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E184" s="12">
-        <f>IF(C184="";"";C184*D184)</f>
+        <f>IF(C184="","",C184*D184)</f>
         <v/>
       </c>
     </row>
@@ -5340,9 +5415,12 @@
         </is>
       </c>
       <c r="C185" s="11" t="n"/>
-      <c r="D185" s="11" t="n"/>
+      <c r="D185" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E185" s="12">
-        <f>IF(C185="";"";C185*D185)</f>
+        <f>IF(C185="","",C185*D185)</f>
         <v/>
       </c>
     </row>
@@ -5356,9 +5434,12 @@
         </is>
       </c>
       <c r="C186" s="11" t="n"/>
-      <c r="D186" s="11" t="n"/>
+      <c r="D186" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E186" s="12">
-        <f>IF(C186="";"";C186*D186)</f>
+        <f>IF(C186="","",C186*D186)</f>
         <v/>
       </c>
     </row>
@@ -5372,9 +5453,12 @@
         </is>
       </c>
       <c r="C187" s="11" t="n"/>
-      <c r="D187" s="11" t="n"/>
+      <c r="D187" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E187" s="12">
-        <f>IF(C187="";"";C187*D187)</f>
+        <f>IF(C187="","",C187*D187)</f>
         <v/>
       </c>
     </row>
@@ -5388,9 +5472,12 @@
         </is>
       </c>
       <c r="C188" s="11" t="n"/>
-      <c r="D188" s="11" t="n"/>
+      <c r="D188" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E188" s="12">
-        <f>IF(C188="";"";C188*D188)</f>
+        <f>IF(C188="","",C188*D188)</f>
         <v/>
       </c>
     </row>
@@ -5404,9 +5491,12 @@
         </is>
       </c>
       <c r="C189" s="11" t="n"/>
-      <c r="D189" s="11" t="n"/>
+      <c r="D189" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E189" s="12">
-        <f>IF(C189="";"";C189*D189)</f>
+        <f>IF(C189="","",C189*D189)</f>
         <v/>
       </c>
     </row>
@@ -5420,9 +5510,12 @@
         </is>
       </c>
       <c r="C190" s="11" t="n"/>
-      <c r="D190" s="11" t="n"/>
+      <c r="D190" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E190" s="12">
-        <f>IF(C190="";"";C190*D190)</f>
+        <f>IF(C190="","",C190*D190)</f>
         <v/>
       </c>
     </row>
@@ -5436,9 +5529,12 @@
         </is>
       </c>
       <c r="C191" s="11" t="n"/>
-      <c r="D191" s="11" t="n"/>
+      <c r="D191" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E191" s="12">
-        <f>IF(C191="";"";C191*D191)</f>
+        <f>IF(C191="","",C191*D191)</f>
         <v/>
       </c>
     </row>
@@ -5452,9 +5548,12 @@
         </is>
       </c>
       <c r="C192" s="11" t="n"/>
-      <c r="D192" s="11" t="n"/>
+      <c r="D192" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E192" s="12">
-        <f>IF(C192="";"";C192*D192)</f>
+        <f>IF(C192="","",C192*D192)</f>
         <v/>
       </c>
     </row>
@@ -5468,9 +5567,12 @@
         </is>
       </c>
       <c r="C193" s="11" t="n"/>
-      <c r="D193" s="11" t="n"/>
+      <c r="D193" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E193" s="12">
-        <f>IF(C193="";"";C193*D193)</f>
+        <f>IF(C193="","",C193*D193)</f>
         <v/>
       </c>
     </row>
@@ -5484,9 +5586,12 @@
         </is>
       </c>
       <c r="C194" s="11" t="n"/>
-      <c r="D194" s="11" t="n"/>
+      <c r="D194" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E194" s="12">
-        <f>IF(C194="";"";C194*D194)</f>
+        <f>IF(C194="","",C194*D194)</f>
         <v/>
       </c>
     </row>
@@ -5500,9 +5605,12 @@
         </is>
       </c>
       <c r="C195" s="11" t="n"/>
-      <c r="D195" s="11" t="n"/>
+      <c r="D195" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E195" s="12">
-        <f>IF(C195="";"";C195*D195)</f>
+        <f>IF(C195="","",C195*D195)</f>
         <v/>
       </c>
     </row>
@@ -5516,9 +5624,12 @@
         </is>
       </c>
       <c r="C196" s="11" t="n"/>
-      <c r="D196" s="11" t="n"/>
+      <c r="D196" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E196" s="12">
-        <f>IF(C196="";"";C196*D196)</f>
+        <f>IF(C196="","",C196*D196)</f>
         <v/>
       </c>
     </row>
@@ -5532,9 +5643,12 @@
         </is>
       </c>
       <c r="C197" s="11" t="n"/>
-      <c r="D197" s="11" t="n"/>
+      <c r="D197" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E197" s="12">
-        <f>IF(C197="";"";C197*D197)</f>
+        <f>IF(C197="","",C197*D197)</f>
         <v/>
       </c>
     </row>
@@ -5548,9 +5662,12 @@
         </is>
       </c>
       <c r="C198" s="11" t="n"/>
-      <c r="D198" s="11" t="n"/>
+      <c r="D198" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E198" s="12">
-        <f>IF(C198="";"";C198*D198)</f>
+        <f>IF(C198="","",C198*D198)</f>
         <v/>
       </c>
     </row>
@@ -5564,9 +5681,12 @@
         </is>
       </c>
       <c r="C199" s="11" t="n"/>
-      <c r="D199" s="11" t="n"/>
+      <c r="D199" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E199" s="12">
-        <f>IF(C199="";"";C199*D199)</f>
+        <f>IF(C199="","",C199*D199)</f>
         <v/>
       </c>
     </row>
@@ -5580,9 +5700,12 @@
         </is>
       </c>
       <c r="C200" s="11" t="n"/>
-      <c r="D200" s="11" t="n"/>
+      <c r="D200" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E200" s="12">
-        <f>IF(C200="";"";C200*D200)</f>
+        <f>IF(C200="","",C200*D200)</f>
         <v/>
       </c>
     </row>
@@ -5596,9 +5719,12 @@
         </is>
       </c>
       <c r="C201" s="11" t="n"/>
-      <c r="D201" s="11" t="n"/>
+      <c r="D201" s="29">
+        <f>Aannames!B28</f>
+        <v/>
+      </c>
       <c r="E201" s="12">
-        <f>IF(C201="";"";C201*D201)</f>
+        <f>IF(C201="","",C201*D201)</f>
         <v/>
       </c>
     </row>
@@ -5619,6 +5745,7 @@
         <v/>
       </c>
     </row>
+    <row r="203"/>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
@@ -5664,11 +5791,11 @@
       </c>
       <c r="C206" s="11" t="n"/>
       <c r="D206" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E206" s="12">
-        <f>IF(C206="";"";C206*D206)</f>
+        <f>IF(C206="","",C206*D206)</f>
         <v/>
       </c>
     </row>
@@ -5683,11 +5810,11 @@
       </c>
       <c r="C207" s="11" t="n"/>
       <c r="D207" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E207" s="12">
-        <f>IF(C207="";"";C207*D207)</f>
+        <f>IF(C207="","",C207*D207)</f>
         <v/>
       </c>
     </row>
@@ -5702,11 +5829,11 @@
       </c>
       <c r="C208" s="11" t="n"/>
       <c r="D208" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E208" s="12">
-        <f>IF(C208="";"";C208*D208)</f>
+        <f>IF(C208="","",C208*D208)</f>
         <v/>
       </c>
     </row>
@@ -5721,11 +5848,11 @@
       </c>
       <c r="C209" s="11" t="n"/>
       <c r="D209" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E209" s="12">
-        <f>IF(C209="";"";C209*D209)</f>
+        <f>IF(C209="","",C209*D209)</f>
         <v/>
       </c>
     </row>
@@ -5740,11 +5867,11 @@
       </c>
       <c r="C210" s="11" t="n"/>
       <c r="D210" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E210" s="12">
-        <f>IF(C210="";"";C210*D210)</f>
+        <f>IF(C210="","",C210*D210)</f>
         <v/>
       </c>
     </row>
@@ -5759,11 +5886,11 @@
       </c>
       <c r="C211" s="11" t="n"/>
       <c r="D211" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E211" s="12">
-        <f>IF(C211="";"";C211*D211)</f>
+        <f>IF(C211="","",C211*D211)</f>
         <v/>
       </c>
     </row>
@@ -5778,11 +5905,11 @@
       </c>
       <c r="C212" s="11" t="n"/>
       <c r="D212" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E212" s="12">
-        <f>IF(C212="";"";C212*D212)</f>
+        <f>IF(C212="","",C212*D212)</f>
         <v/>
       </c>
     </row>
@@ -5797,11 +5924,11 @@
       </c>
       <c r="C213" s="11" t="n"/>
       <c r="D213" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E213" s="12">
-        <f>IF(C213="";"";C213*D213)</f>
+        <f>IF(C213="","",C213*D213)</f>
         <v/>
       </c>
     </row>
@@ -5816,11 +5943,11 @@
       </c>
       <c r="C214" s="11" t="n"/>
       <c r="D214" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E214" s="12">
-        <f>IF(C214="";"";C214*D214)</f>
+        <f>IF(C214="","",C214*D214)</f>
         <v/>
       </c>
     </row>
@@ -5835,11 +5962,11 @@
       </c>
       <c r="C215" s="11" t="n"/>
       <c r="D215" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E215" s="12">
-        <f>IF(C215="";"";C215*D215)</f>
+        <f>IF(C215="","",C215*D215)</f>
         <v/>
       </c>
     </row>
@@ -5854,11 +5981,11 @@
       </c>
       <c r="C216" s="11" t="n"/>
       <c r="D216" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E216" s="12">
-        <f>IF(C216="";"";C216*D216)</f>
+        <f>IF(C216="","",C216*D216)</f>
         <v/>
       </c>
     </row>
@@ -5873,11 +6000,11 @@
       </c>
       <c r="C217" s="11" t="n"/>
       <c r="D217" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E217" s="12">
-        <f>IF(C217="";"";C217*D217)</f>
+        <f>IF(C217="","",C217*D217)</f>
         <v/>
       </c>
     </row>
@@ -5892,11 +6019,11 @@
       </c>
       <c r="C218" s="11" t="n"/>
       <c r="D218" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E218" s="12">
-        <f>IF(C218="";"";C218*D218)</f>
+        <f>IF(C218="","",C218*D218)</f>
         <v/>
       </c>
     </row>
@@ -5911,11 +6038,11 @@
       </c>
       <c r="C219" s="11" t="n"/>
       <c r="D219" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E219" s="12">
-        <f>IF(C219="";"";C219*D219)</f>
+        <f>IF(C219="","",C219*D219)</f>
         <v/>
       </c>
     </row>
@@ -5930,11 +6057,11 @@
       </c>
       <c r="C220" s="11" t="n"/>
       <c r="D220" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E220" s="12">
-        <f>IF(C220="";"";C220*D220)</f>
+        <f>IF(C220="","",C220*D220)</f>
         <v/>
       </c>
     </row>
@@ -5949,11 +6076,11 @@
       </c>
       <c r="C221" s="11" t="n"/>
       <c r="D221" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E221" s="12">
-        <f>IF(C221="";"";C221*D221)</f>
+        <f>IF(C221="","",C221*D221)</f>
         <v/>
       </c>
     </row>
@@ -5968,11 +6095,11 @@
       </c>
       <c r="C222" s="11" t="n"/>
       <c r="D222" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E222" s="12">
-        <f>IF(C222="";"";C222*D222)</f>
+        <f>IF(C222="","",C222*D222)</f>
         <v/>
       </c>
     </row>
@@ -5987,11 +6114,11 @@
       </c>
       <c r="C223" s="11" t="n"/>
       <c r="D223" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E223" s="12">
-        <f>IF(C223="";"";C223*D223)</f>
+        <f>IF(C223="","",C223*D223)</f>
         <v/>
       </c>
     </row>
@@ -6006,11 +6133,11 @@
       </c>
       <c r="C224" s="11" t="n"/>
       <c r="D224" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E224" s="12">
-        <f>IF(C224="";"";C224*D224)</f>
+        <f>IF(C224="","",C224*D224)</f>
         <v/>
       </c>
     </row>
@@ -6025,11 +6152,11 @@
       </c>
       <c r="C225" s="11" t="n"/>
       <c r="D225" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E225" s="12">
-        <f>IF(C225="";"";C225*D225)</f>
+        <f>IF(C225="","",C225*D225)</f>
         <v/>
       </c>
     </row>
@@ -6044,11 +6171,11 @@
       </c>
       <c r="C226" s="11" t="n"/>
       <c r="D226" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E226" s="12">
-        <f>IF(C226="";"";C226*D226)</f>
+        <f>IF(C226="","",C226*D226)</f>
         <v/>
       </c>
     </row>
@@ -6063,11 +6190,11 @@
       </c>
       <c r="C227" s="11" t="n"/>
       <c r="D227" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E227" s="12">
-        <f>IF(C227="";"";C227*D227)</f>
+        <f>IF(C227="","",C227*D227)</f>
         <v/>
       </c>
     </row>
@@ -6082,11 +6209,11 @@
       </c>
       <c r="C228" s="11" t="n"/>
       <c r="D228" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E228" s="12">
-        <f>IF(C228="";"";C228*D228)</f>
+        <f>IF(C228="","",C228*D228)</f>
         <v/>
       </c>
     </row>
@@ -6101,11 +6228,11 @@
       </c>
       <c r="C229" s="11" t="n"/>
       <c r="D229" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E229" s="12">
-        <f>IF(C229="";"";C229*D229)</f>
+        <f>IF(C229="","",C229*D229)</f>
         <v/>
       </c>
     </row>
@@ -6120,11 +6247,11 @@
       </c>
       <c r="C230" s="11" t="n"/>
       <c r="D230" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E230" s="12">
-        <f>IF(C230="";"";C230*D230)</f>
+        <f>IF(C230="","",C230*D230)</f>
         <v/>
       </c>
     </row>
@@ -6139,11 +6266,11 @@
       </c>
       <c r="C231" s="11" t="n"/>
       <c r="D231" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E231" s="12">
-        <f>IF(C231="";"";C231*D231)</f>
+        <f>IF(C231="","",C231*D231)</f>
         <v/>
       </c>
     </row>
@@ -6158,11 +6285,11 @@
       </c>
       <c r="C232" s="11" t="n"/>
       <c r="D232" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E232" s="12">
-        <f>IF(C232="";"";C232*D232)</f>
+        <f>IF(C232="","",C232*D232)</f>
         <v/>
       </c>
     </row>
@@ -6177,11 +6304,11 @@
       </c>
       <c r="C233" s="11" t="n"/>
       <c r="D233" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E233" s="12">
-        <f>IF(C233="";"";C233*D233)</f>
+        <f>IF(C233="","",C233*D233)</f>
         <v/>
       </c>
     </row>
@@ -6196,11 +6323,11 @@
       </c>
       <c r="C234" s="11" t="n"/>
       <c r="D234" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E234" s="12">
-        <f>IF(C234="";"";C234*D234)</f>
+        <f>IF(C234="","",C234*D234)</f>
         <v/>
       </c>
     </row>
@@ -6215,11 +6342,11 @@
       </c>
       <c r="C235" s="11" t="n"/>
       <c r="D235" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E235" s="12">
-        <f>IF(C235="";"";C235*D235)</f>
+        <f>IF(C235="","",C235*D235)</f>
         <v/>
       </c>
     </row>
@@ -6234,11 +6361,11 @@
       </c>
       <c r="C236" s="11" t="n"/>
       <c r="D236" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E236" s="12">
-        <f>IF(C236="";"";C236*D236)</f>
+        <f>IF(C236="","",C236*D236)</f>
         <v/>
       </c>
     </row>
@@ -6253,11 +6380,11 @@
       </c>
       <c r="C237" s="11" t="n"/>
       <c r="D237" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E237" s="12">
-        <f>IF(C237="";"";C237*D237)</f>
+        <f>IF(C237="","",C237*D237)</f>
         <v/>
       </c>
     </row>
@@ -6272,11 +6399,11 @@
       </c>
       <c r="C238" s="11" t="n"/>
       <c r="D238" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E238" s="12">
-        <f>IF(C238="";"";C238*D238)</f>
+        <f>IF(C238="","",C238*D238)</f>
         <v/>
       </c>
     </row>
@@ -6291,11 +6418,11 @@
       </c>
       <c r="C239" s="11" t="n"/>
       <c r="D239" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E239" s="12">
-        <f>IF(C239="";"";C239*D239)</f>
+        <f>IF(C239="","",C239*D239)</f>
         <v/>
       </c>
     </row>
@@ -6310,11 +6437,11 @@
       </c>
       <c r="C240" s="11" t="n"/>
       <c r="D240" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E240" s="12">
-        <f>IF(C240="";"";C240*D240)</f>
+        <f>IF(C240="","",C240*D240)</f>
         <v/>
       </c>
     </row>
@@ -6329,11 +6456,11 @@
       </c>
       <c r="C241" s="11" t="n"/>
       <c r="D241" s="12">
-        <f>Aannames!B34</f>
+        <f>Aannames!B31</f>
         <v/>
       </c>
       <c r="E241" s="12">
-        <f>IF(C241="";"";C241*D241)</f>
+        <f>IF(C241="","",C241*D241)</f>
         <v/>
       </c>
     </row>
@@ -6354,6 +6481,8 @@
         <v/>
       </c>
     </row>
+    <row r="243"/>
+    <row r="244"/>
     <row r="245">
       <c r="A245" s="16" t="inlineStr">
         <is>
@@ -6438,6 +6567,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr"/>
       <c r="B3" s="10" t="inlineStr">
@@ -6671,147 +6801,147 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>IFERROR('Verkoopprognose'!E6;0)</f>
+        <f>IFERROR('Verkoopprognose'!E6,0)</f>
         <v/>
       </c>
       <c r="C5" s="12">
-        <f>IFERROR('Verkoopprognose'!E7;0)</f>
+        <f>IFERROR('Verkoopprognose'!E7,0)</f>
         <v/>
       </c>
       <c r="D5" s="12">
-        <f>IFERROR('Verkoopprognose'!E8;0)</f>
+        <f>IFERROR('Verkoopprognose'!E8,0)</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>IFERROR('Verkoopprognose'!E9;0)</f>
+        <f>IFERROR('Verkoopprognose'!E9,0)</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR('Verkoopprognose'!E10;0)</f>
+        <f>IFERROR('Verkoopprognose'!E10,0)</f>
         <v/>
       </c>
       <c r="G5" s="12">
-        <f>IFERROR('Verkoopprognose'!E11;0)</f>
+        <f>IFERROR('Verkoopprognose'!E11,0)</f>
         <v/>
       </c>
       <c r="H5" s="12">
-        <f>IFERROR('Verkoopprognose'!E12;0)</f>
+        <f>IFERROR('Verkoopprognose'!E12,0)</f>
         <v/>
       </c>
       <c r="I5" s="12">
-        <f>IFERROR('Verkoopprognose'!E13;0)</f>
+        <f>IFERROR('Verkoopprognose'!E13,0)</f>
         <v/>
       </c>
       <c r="J5" s="12">
-        <f>IFERROR('Verkoopprognose'!E14;0)</f>
+        <f>IFERROR('Verkoopprognose'!E14,0)</f>
         <v/>
       </c>
       <c r="K5" s="12">
-        <f>IFERROR('Verkoopprognose'!E15;0)</f>
+        <f>IFERROR('Verkoopprognose'!E15,0)</f>
         <v/>
       </c>
       <c r="L5" s="12">
-        <f>IFERROR('Verkoopprognose'!E16;0)</f>
+        <f>IFERROR('Verkoopprognose'!E16,0)</f>
         <v/>
       </c>
       <c r="M5" s="12">
-        <f>IFERROR('Verkoopprognose'!E17;0)</f>
+        <f>IFERROR('Verkoopprognose'!E17,0)</f>
         <v/>
       </c>
       <c r="N5" s="12">
-        <f>IFERROR('Verkoopprognose'!E18;0)</f>
+        <f>IFERROR('Verkoopprognose'!E18,0)</f>
         <v/>
       </c>
       <c r="O5" s="12">
-        <f>IFERROR('Verkoopprognose'!E19;0)</f>
+        <f>IFERROR('Verkoopprognose'!E19,0)</f>
         <v/>
       </c>
       <c r="P5" s="12">
-        <f>IFERROR('Verkoopprognose'!E20;0)</f>
+        <f>IFERROR('Verkoopprognose'!E20,0)</f>
         <v/>
       </c>
       <c r="Q5" s="12">
-        <f>IFERROR('Verkoopprognose'!E21;0)</f>
+        <f>IFERROR('Verkoopprognose'!E21,0)</f>
         <v/>
       </c>
       <c r="R5" s="12">
-        <f>IFERROR('Verkoopprognose'!E22;0)</f>
+        <f>IFERROR('Verkoopprognose'!E22,0)</f>
         <v/>
       </c>
       <c r="S5" s="12">
-        <f>IFERROR('Verkoopprognose'!E23;0)</f>
+        <f>IFERROR('Verkoopprognose'!E23,0)</f>
         <v/>
       </c>
       <c r="T5" s="12">
-        <f>IFERROR('Verkoopprognose'!E24;0)</f>
+        <f>IFERROR('Verkoopprognose'!E24,0)</f>
         <v/>
       </c>
       <c r="U5" s="12">
-        <f>IFERROR('Verkoopprognose'!E25;0)</f>
+        <f>IFERROR('Verkoopprognose'!E25,0)</f>
         <v/>
       </c>
       <c r="V5" s="12">
-        <f>IFERROR('Verkoopprognose'!E26;0)</f>
+        <f>IFERROR('Verkoopprognose'!E26,0)</f>
         <v/>
       </c>
       <c r="W5" s="12">
-        <f>IFERROR('Verkoopprognose'!E27;0)</f>
+        <f>IFERROR('Verkoopprognose'!E27,0)</f>
         <v/>
       </c>
       <c r="X5" s="12">
-        <f>IFERROR('Verkoopprognose'!E28;0)</f>
+        <f>IFERROR('Verkoopprognose'!E28,0)</f>
         <v/>
       </c>
       <c r="Y5" s="12">
-        <f>IFERROR('Verkoopprognose'!E29;0)</f>
+        <f>IFERROR('Verkoopprognose'!E29,0)</f>
         <v/>
       </c>
       <c r="Z5" s="12">
-        <f>IFERROR('Verkoopprognose'!E30;0)</f>
+        <f>IFERROR('Verkoopprognose'!E30,0)</f>
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>IFERROR('Verkoopprognose'!E31;0)</f>
+        <f>IFERROR('Verkoopprognose'!E31,0)</f>
         <v/>
       </c>
       <c r="AB5" s="12">
-        <f>IFERROR('Verkoopprognose'!E32;0)</f>
+        <f>IFERROR('Verkoopprognose'!E32,0)</f>
         <v/>
       </c>
       <c r="AC5" s="12">
-        <f>IFERROR('Verkoopprognose'!E33;0)</f>
+        <f>IFERROR('Verkoopprognose'!E33,0)</f>
         <v/>
       </c>
       <c r="AD5" s="12">
-        <f>IFERROR('Verkoopprognose'!E34;0)</f>
+        <f>IFERROR('Verkoopprognose'!E34,0)</f>
         <v/>
       </c>
       <c r="AE5" s="12">
-        <f>IFERROR('Verkoopprognose'!E35;0)</f>
+        <f>IFERROR('Verkoopprognose'!E35,0)</f>
         <v/>
       </c>
       <c r="AF5" s="12">
-        <f>IFERROR('Verkoopprognose'!E36;0)</f>
+        <f>IFERROR('Verkoopprognose'!E36,0)</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IFERROR('Verkoopprognose'!E37;0)</f>
+        <f>IFERROR('Verkoopprognose'!E37,0)</f>
         <v/>
       </c>
       <c r="AH5" s="12">
-        <f>IFERROR('Verkoopprognose'!E38;0)</f>
+        <f>IFERROR('Verkoopprognose'!E38,0)</f>
         <v/>
       </c>
       <c r="AI5" s="12">
-        <f>IFERROR('Verkoopprognose'!E39;0)</f>
+        <f>IFERROR('Verkoopprognose'!E39,0)</f>
         <v/>
       </c>
       <c r="AJ5" s="12">
-        <f>IFERROR('Verkoopprognose'!E40;0)</f>
+        <f>IFERROR('Verkoopprognose'!E40,0)</f>
         <v/>
       </c>
       <c r="AK5" s="12">
-        <f>IFERROR('Verkoopprognose'!E41;0)</f>
+        <f>IFERROR('Verkoopprognose'!E41,0)</f>
         <v/>
       </c>
     </row>
@@ -6822,147 +6952,147 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>IFERROR('Verkoopprognose'!E46;0)</f>
+        <f>IFERROR('Verkoopprognose'!E46,0)</f>
         <v/>
       </c>
       <c r="C6" s="12">
-        <f>IFERROR('Verkoopprognose'!E47;0)</f>
+        <f>IFERROR('Verkoopprognose'!E47,0)</f>
         <v/>
       </c>
       <c r="D6" s="12">
-        <f>IFERROR('Verkoopprognose'!E48;0)</f>
+        <f>IFERROR('Verkoopprognose'!E48,0)</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>IFERROR('Verkoopprognose'!E49;0)</f>
+        <f>IFERROR('Verkoopprognose'!E49,0)</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR('Verkoopprognose'!E50;0)</f>
+        <f>IFERROR('Verkoopprognose'!E50,0)</f>
         <v/>
       </c>
       <c r="G6" s="12">
-        <f>IFERROR('Verkoopprognose'!E51;0)</f>
+        <f>IFERROR('Verkoopprognose'!E51,0)</f>
         <v/>
       </c>
       <c r="H6" s="12">
-        <f>IFERROR('Verkoopprognose'!E52;0)</f>
+        <f>IFERROR('Verkoopprognose'!E52,0)</f>
         <v/>
       </c>
       <c r="I6" s="12">
-        <f>IFERROR('Verkoopprognose'!E53;0)</f>
+        <f>IFERROR('Verkoopprognose'!E53,0)</f>
         <v/>
       </c>
       <c r="J6" s="12">
-        <f>IFERROR('Verkoopprognose'!E54;0)</f>
+        <f>IFERROR('Verkoopprognose'!E54,0)</f>
         <v/>
       </c>
       <c r="K6" s="12">
-        <f>IFERROR('Verkoopprognose'!E55;0)</f>
+        <f>IFERROR('Verkoopprognose'!E55,0)</f>
         <v/>
       </c>
       <c r="L6" s="12">
-        <f>IFERROR('Verkoopprognose'!E56;0)</f>
+        <f>IFERROR('Verkoopprognose'!E56,0)</f>
         <v/>
       </c>
       <c r="M6" s="12">
-        <f>IFERROR('Verkoopprognose'!E57;0)</f>
+        <f>IFERROR('Verkoopprognose'!E57,0)</f>
         <v/>
       </c>
       <c r="N6" s="12">
-        <f>IFERROR('Verkoopprognose'!E58;0)</f>
+        <f>IFERROR('Verkoopprognose'!E58,0)</f>
         <v/>
       </c>
       <c r="O6" s="12">
-        <f>IFERROR('Verkoopprognose'!E59;0)</f>
+        <f>IFERROR('Verkoopprognose'!E59,0)</f>
         <v/>
       </c>
       <c r="P6" s="12">
-        <f>IFERROR('Verkoopprognose'!E60;0)</f>
+        <f>IFERROR('Verkoopprognose'!E60,0)</f>
         <v/>
       </c>
       <c r="Q6" s="12">
-        <f>IFERROR('Verkoopprognose'!E61;0)</f>
+        <f>IFERROR('Verkoopprognose'!E61,0)</f>
         <v/>
       </c>
       <c r="R6" s="12">
-        <f>IFERROR('Verkoopprognose'!E62;0)</f>
+        <f>IFERROR('Verkoopprognose'!E62,0)</f>
         <v/>
       </c>
       <c r="S6" s="12">
-        <f>IFERROR('Verkoopprognose'!E63;0)</f>
+        <f>IFERROR('Verkoopprognose'!E63,0)</f>
         <v/>
       </c>
       <c r="T6" s="12">
-        <f>IFERROR('Verkoopprognose'!E64;0)</f>
+        <f>IFERROR('Verkoopprognose'!E64,0)</f>
         <v/>
       </c>
       <c r="U6" s="12">
-        <f>IFERROR('Verkoopprognose'!E65;0)</f>
+        <f>IFERROR('Verkoopprognose'!E65,0)</f>
         <v/>
       </c>
       <c r="V6" s="12">
-        <f>IFERROR('Verkoopprognose'!E66;0)</f>
+        <f>IFERROR('Verkoopprognose'!E66,0)</f>
         <v/>
       </c>
       <c r="W6" s="12">
-        <f>IFERROR('Verkoopprognose'!E67;0)</f>
+        <f>IFERROR('Verkoopprognose'!E67,0)</f>
         <v/>
       </c>
       <c r="X6" s="12">
-        <f>IFERROR('Verkoopprognose'!E68;0)</f>
+        <f>IFERROR('Verkoopprognose'!E68,0)</f>
         <v/>
       </c>
       <c r="Y6" s="12">
-        <f>IFERROR('Verkoopprognose'!E69;0)</f>
+        <f>IFERROR('Verkoopprognose'!E69,0)</f>
         <v/>
       </c>
       <c r="Z6" s="12">
-        <f>IFERROR('Verkoopprognose'!E70;0)</f>
+        <f>IFERROR('Verkoopprognose'!E70,0)</f>
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>IFERROR('Verkoopprognose'!E71;0)</f>
+        <f>IFERROR('Verkoopprognose'!E71,0)</f>
         <v/>
       </c>
       <c r="AB6" s="12">
-        <f>IFERROR('Verkoopprognose'!E72;0)</f>
+        <f>IFERROR('Verkoopprognose'!E72,0)</f>
         <v/>
       </c>
       <c r="AC6" s="12">
-        <f>IFERROR('Verkoopprognose'!E73;0)</f>
+        <f>IFERROR('Verkoopprognose'!E73,0)</f>
         <v/>
       </c>
       <c r="AD6" s="12">
-        <f>IFERROR('Verkoopprognose'!E74;0)</f>
+        <f>IFERROR('Verkoopprognose'!E74,0)</f>
         <v/>
       </c>
       <c r="AE6" s="12">
-        <f>IFERROR('Verkoopprognose'!E75;0)</f>
+        <f>IFERROR('Verkoopprognose'!E75,0)</f>
         <v/>
       </c>
       <c r="AF6" s="12">
-        <f>IFERROR('Verkoopprognose'!E76;0)</f>
+        <f>IFERROR('Verkoopprognose'!E76,0)</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IFERROR('Verkoopprognose'!E77;0)</f>
+        <f>IFERROR('Verkoopprognose'!E77,0)</f>
         <v/>
       </c>
       <c r="AH6" s="12">
-        <f>IFERROR('Verkoopprognose'!E78;0)</f>
+        <f>IFERROR('Verkoopprognose'!E78,0)</f>
         <v/>
       </c>
       <c r="AI6" s="12">
-        <f>IFERROR('Verkoopprognose'!E79;0)</f>
+        <f>IFERROR('Verkoopprognose'!E79,0)</f>
         <v/>
       </c>
       <c r="AJ6" s="12">
-        <f>IFERROR('Verkoopprognose'!E80;0)</f>
+        <f>IFERROR('Verkoopprognose'!E80,0)</f>
         <v/>
       </c>
       <c r="AK6" s="12">
-        <f>IFERROR('Verkoopprognose'!E81;0)</f>
+        <f>IFERROR('Verkoopprognose'!E81,0)</f>
         <v/>
       </c>
     </row>
@@ -6973,147 +7103,147 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>IFERROR('Verkoopprognose'!E86;0)</f>
+        <f>IFERROR('Verkoopprognose'!E86,0)</f>
         <v/>
       </c>
       <c r="C7" s="12">
-        <f>IFERROR('Verkoopprognose'!E87;0)</f>
+        <f>IFERROR('Verkoopprognose'!E87,0)</f>
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>IFERROR('Verkoopprognose'!E88;0)</f>
+        <f>IFERROR('Verkoopprognose'!E88,0)</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>IFERROR('Verkoopprognose'!E89;0)</f>
+        <f>IFERROR('Verkoopprognose'!E89,0)</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR('Verkoopprognose'!E90;0)</f>
+        <f>IFERROR('Verkoopprognose'!E90,0)</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>IFERROR('Verkoopprognose'!E91;0)</f>
+        <f>IFERROR('Verkoopprognose'!E91,0)</f>
         <v/>
       </c>
       <c r="H7" s="12">
-        <f>IFERROR('Verkoopprognose'!E92;0)</f>
+        <f>IFERROR('Verkoopprognose'!E92,0)</f>
         <v/>
       </c>
       <c r="I7" s="12">
-        <f>IFERROR('Verkoopprognose'!E93;0)</f>
+        <f>IFERROR('Verkoopprognose'!E93,0)</f>
         <v/>
       </c>
       <c r="J7" s="12">
-        <f>IFERROR('Verkoopprognose'!E94;0)</f>
+        <f>IFERROR('Verkoopprognose'!E94,0)</f>
         <v/>
       </c>
       <c r="K7" s="12">
-        <f>IFERROR('Verkoopprognose'!E95;0)</f>
+        <f>IFERROR('Verkoopprognose'!E95,0)</f>
         <v/>
       </c>
       <c r="L7" s="12">
-        <f>IFERROR('Verkoopprognose'!E96;0)</f>
+        <f>IFERROR('Verkoopprognose'!E96,0)</f>
         <v/>
       </c>
       <c r="M7" s="12">
-        <f>IFERROR('Verkoopprognose'!E97;0)</f>
+        <f>IFERROR('Verkoopprognose'!E97,0)</f>
         <v/>
       </c>
       <c r="N7" s="12">
-        <f>IFERROR('Verkoopprognose'!E98;0)</f>
+        <f>IFERROR('Verkoopprognose'!E98,0)</f>
         <v/>
       </c>
       <c r="O7" s="12">
-        <f>IFERROR('Verkoopprognose'!E99;0)</f>
+        <f>IFERROR('Verkoopprognose'!E99,0)</f>
         <v/>
       </c>
       <c r="P7" s="12">
-        <f>IFERROR('Verkoopprognose'!E100;0)</f>
+        <f>IFERROR('Verkoopprognose'!E100,0)</f>
         <v/>
       </c>
       <c r="Q7" s="12">
-        <f>IFERROR('Verkoopprognose'!E101;0)</f>
+        <f>IFERROR('Verkoopprognose'!E101,0)</f>
         <v/>
       </c>
       <c r="R7" s="12">
-        <f>IFERROR('Verkoopprognose'!E102;0)</f>
+        <f>IFERROR('Verkoopprognose'!E102,0)</f>
         <v/>
       </c>
       <c r="S7" s="12">
-        <f>IFERROR('Verkoopprognose'!E103;0)</f>
+        <f>IFERROR('Verkoopprognose'!E103,0)</f>
         <v/>
       </c>
       <c r="T7" s="12">
-        <f>IFERROR('Verkoopprognose'!E104;0)</f>
+        <f>IFERROR('Verkoopprognose'!E104,0)</f>
         <v/>
       </c>
       <c r="U7" s="12">
-        <f>IFERROR('Verkoopprognose'!E105;0)</f>
+        <f>IFERROR('Verkoopprognose'!E105,0)</f>
         <v/>
       </c>
       <c r="V7" s="12">
-        <f>IFERROR('Verkoopprognose'!E106;0)</f>
+        <f>IFERROR('Verkoopprognose'!E106,0)</f>
         <v/>
       </c>
       <c r="W7" s="12">
-        <f>IFERROR('Verkoopprognose'!E107;0)</f>
+        <f>IFERROR('Verkoopprognose'!E107,0)</f>
         <v/>
       </c>
       <c r="X7" s="12">
-        <f>IFERROR('Verkoopprognose'!E108;0)</f>
+        <f>IFERROR('Verkoopprognose'!E108,0)</f>
         <v/>
       </c>
       <c r="Y7" s="12">
-        <f>IFERROR('Verkoopprognose'!E109;0)</f>
+        <f>IFERROR('Verkoopprognose'!E109,0)</f>
         <v/>
       </c>
       <c r="Z7" s="12">
-        <f>IFERROR('Verkoopprognose'!E110;0)</f>
+        <f>IFERROR('Verkoopprognose'!E110,0)</f>
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>IFERROR('Verkoopprognose'!E111;0)</f>
+        <f>IFERROR('Verkoopprognose'!E111,0)</f>
         <v/>
       </c>
       <c r="AB7" s="12">
-        <f>IFERROR('Verkoopprognose'!E112;0)</f>
+        <f>IFERROR('Verkoopprognose'!E112,0)</f>
         <v/>
       </c>
       <c r="AC7" s="12">
-        <f>IFERROR('Verkoopprognose'!E113;0)</f>
+        <f>IFERROR('Verkoopprognose'!E113,0)</f>
         <v/>
       </c>
       <c r="AD7" s="12">
-        <f>IFERROR('Verkoopprognose'!E114;0)</f>
+        <f>IFERROR('Verkoopprognose'!E114,0)</f>
         <v/>
       </c>
       <c r="AE7" s="12">
-        <f>IFERROR('Verkoopprognose'!E115;0)</f>
+        <f>IFERROR('Verkoopprognose'!E115,0)</f>
         <v/>
       </c>
       <c r="AF7" s="12">
-        <f>IFERROR('Verkoopprognose'!E116;0)</f>
+        <f>IFERROR('Verkoopprognose'!E116,0)</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IFERROR('Verkoopprognose'!E117;0)</f>
+        <f>IFERROR('Verkoopprognose'!E117,0)</f>
         <v/>
       </c>
       <c r="AH7" s="12">
-        <f>IFERROR('Verkoopprognose'!E118;0)</f>
+        <f>IFERROR('Verkoopprognose'!E118,0)</f>
         <v/>
       </c>
       <c r="AI7" s="12">
-        <f>IFERROR('Verkoopprognose'!E119;0)</f>
+        <f>IFERROR('Verkoopprognose'!E119,0)</f>
         <v/>
       </c>
       <c r="AJ7" s="12">
-        <f>IFERROR('Verkoopprognose'!E120;0)</f>
+        <f>IFERROR('Verkoopprognose'!E120,0)</f>
         <v/>
       </c>
       <c r="AK7" s="12">
-        <f>IFERROR('Verkoopprognose'!E121;0)</f>
+        <f>IFERROR('Verkoopprognose'!E121,0)</f>
         <v/>
       </c>
     </row>
@@ -7124,147 +7254,147 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>IFERROR(SUM(B6:B7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((B6+B7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="C8" s="12">
-        <f>IFERROR(SUM(C6:C7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((C6+C7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>IFERROR(SUM(D6:D7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((D6+D7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>IFERROR(SUM(E6:E7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((E6+E7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(SUM(F6:F7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((F6+F7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>IFERROR(SUM(G6:G7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((G6+G7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="H8" s="12">
-        <f>IFERROR(SUM(H6:H7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((H6+H7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="I8" s="12">
-        <f>IFERROR(SUM(I6:I7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((I6+I7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="J8" s="12">
-        <f>IFERROR(SUM(J6:J7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((J6+J7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="K8" s="12">
-        <f>IFERROR(SUM(K6:K7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((K6+K7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="L8" s="12">
-        <f>IFERROR(SUM(L6:L7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((L6+L7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="M8" s="12">
-        <f>IFERROR(SUM(M6:M7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((M6+M7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="N8" s="12">
-        <f>IFERROR(SUM(N6:N7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((N6+N7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="O8" s="12">
-        <f>IFERROR(SUM(O6:O7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((O6+O7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="P8" s="12">
-        <f>IFERROR(SUM(P6:P7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((P6+P7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="Q8" s="12">
-        <f>IFERROR(SUM(Q6:Q7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((Q6+Q7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="R8" s="12">
-        <f>IFERROR(SUM(R6:R7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((R6+R7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="S8" s="12">
-        <f>IFERROR(SUM(S6:S7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((S6+S7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="T8" s="12">
-        <f>IFERROR(SUM(T6:T7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((T6+T7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="U8" s="12">
-        <f>IFERROR(SUM(U6:U7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((U6+U7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="V8" s="12">
-        <f>IFERROR(SUM(V6:V7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((V6+V7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="W8" s="12">
-        <f>IFERROR(SUM(W6:W7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((W6+W7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="X8" s="12">
-        <f>IFERROR(SUM(X6:X7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((X6+X7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="Y8" s="12">
-        <f>IFERROR(SUM(Y6:Y7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((Y6+Y7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="Z8" s="12">
-        <f>IFERROR(SUM(Z6:Z7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((Z6+Z7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>IFERROR(SUM(AA6:AA7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AA6+AA7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AB8" s="12">
-        <f>IFERROR(SUM(AB6:AB7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AB6+AB7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AC8" s="12">
-        <f>IFERROR(SUM(AC6:AC7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AC6+AC7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AD8" s="12">
-        <f>IFERROR(SUM(AD6:AD7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AD6+AD7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AE8" s="12">
-        <f>IFERROR(SUM(AE6:AE7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AE6+AE7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AF8" s="12">
-        <f>IFERROR(SUM(AF6:AF7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AF6+AF7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IFERROR(SUM(AG6:AG7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AG6+AG7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AH8" s="12">
-        <f>IFERROR(SUM(AH6:AH7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AH6+AH7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AI8" s="12">
-        <f>IFERROR(SUM(AI6:AI7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AI6+AI7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AJ8" s="12">
-        <f>IFERROR(SUM(AJ6:AJ7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AJ6+AJ7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
       <c r="AK8" s="12">
-        <f>IFERROR(SUM(AK6:AK7)*Aannames!B24*Aannames!B23;0)</f>
+        <f>IFERROR((AK6+AK7)*Aannames!B20*Aannames!B21,0)</f>
         <v/>
       </c>
     </row>
@@ -7275,147 +7405,147 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>IFERROR('Verkoopprognose'!C126*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C126*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="C9" s="12">
-        <f>IFERROR('Verkoopprognose'!C127*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C127*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>IFERROR('Verkoopprognose'!C128*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C128*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>IFERROR('Verkoopprognose'!C129*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C129*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR('Verkoopprognose'!C130*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C130*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>IFERROR('Verkoopprognose'!C131*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C131*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>IFERROR('Verkoopprognose'!C132*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C132*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="I9" s="12">
-        <f>IFERROR('Verkoopprognose'!C133*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C133*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="J9" s="12">
-        <f>IFERROR('Verkoopprognose'!C134*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C134*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="K9" s="12">
-        <f>IFERROR('Verkoopprognose'!C135*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C135*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="L9" s="12">
-        <f>IFERROR('Verkoopprognose'!C136*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C136*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="M9" s="12">
-        <f>IFERROR('Verkoopprognose'!C137*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C137*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="N9" s="12">
-        <f>IFERROR('Verkoopprognose'!C138*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C138*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="O9" s="12">
-        <f>IFERROR('Verkoopprognose'!C139*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C139*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="P9" s="12">
-        <f>IFERROR('Verkoopprognose'!C140*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C140*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="Q9" s="12">
-        <f>IFERROR('Verkoopprognose'!C141*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C141*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="R9" s="12">
-        <f>IFERROR('Verkoopprognose'!C142*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C142*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="S9" s="12">
-        <f>IFERROR('Verkoopprognose'!C143*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C143*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="T9" s="12">
-        <f>IFERROR('Verkoopprognose'!C144*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C144*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="U9" s="12">
-        <f>IFERROR('Verkoopprognose'!C145*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C145*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>IFERROR('Verkoopprognose'!C146*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C146*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="W9" s="12">
-        <f>IFERROR('Verkoopprognose'!C147*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C147*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="X9" s="12">
-        <f>IFERROR('Verkoopprognose'!C148*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C148*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="Y9" s="12">
-        <f>IFERROR('Verkoopprognose'!C149*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C149*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="Z9" s="12">
-        <f>IFERROR('Verkoopprognose'!C150*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C150*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>IFERROR('Verkoopprognose'!C151*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C151*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>IFERROR('Verkoopprognose'!C152*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C152*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>IFERROR('Verkoopprognose'!C153*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C153*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AD9" s="12">
-        <f>IFERROR('Verkoopprognose'!C154*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C154*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AE9" s="12">
-        <f>IFERROR('Verkoopprognose'!C155*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C155*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>IFERROR('Verkoopprognose'!C156*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C156*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IFERROR('Verkoopprognose'!C157*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C157*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AH9" s="12">
-        <f>IFERROR('Verkoopprognose'!C158*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C158*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AI9" s="12">
-        <f>IFERROR('Verkoopprognose'!C159*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C159*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AJ9" s="12">
-        <f>IFERROR('Verkoopprognose'!C160*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C160*Aannames!B24,0)</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>IFERROR('Verkoopprognose'!C161*Aannames!B27;0)</f>
+        <f>IFERROR('Verkoopprognose'!C161*Aannames!B24,0)</f>
         <v/>
       </c>
     </row>
@@ -7426,147 +7556,147 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>IFERROR(Aannames!B45*(B5+B6+B7);0)</f>
+        <f>IFERROR(Aannames!B42*(B5+B6+B7),0)</f>
         <v/>
       </c>
       <c r="C10" s="12">
-        <f>IFERROR(Aannames!B45*(C5+C6+C7);0)</f>
+        <f>IFERROR(Aannames!B42*(C5+C6+C7),0)</f>
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>IFERROR(Aannames!B45*(D5+D6+D7);0)</f>
+        <f>IFERROR(Aannames!B42*(D5+D6+D7),0)</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>IFERROR(Aannames!B45*(E5+E6+E7);0)</f>
+        <f>IFERROR(Aannames!B42*(E5+E6+E7),0)</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(Aannames!B45*(F5+F6+F7);0)</f>
+        <f>IFERROR(Aannames!B42*(F5+F6+F7),0)</f>
         <v/>
       </c>
       <c r="G10" s="12">
-        <f>IFERROR(Aannames!B45*(G5+G6+G7);0)</f>
+        <f>IFERROR(Aannames!B42*(G5+G6+G7),0)</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f>IFERROR(Aannames!B45*(H5+H6+H7);0)</f>
+        <f>IFERROR(Aannames!B42*(H5+H6+H7),0)</f>
         <v/>
       </c>
       <c r="I10" s="12">
-        <f>IFERROR(Aannames!B45*(I5+I6+I7);0)</f>
+        <f>IFERROR(Aannames!B42*(I5+I6+I7),0)</f>
         <v/>
       </c>
       <c r="J10" s="12">
-        <f>IFERROR(Aannames!B45*(J5+J6+J7);0)</f>
+        <f>IFERROR(Aannames!B42*(J5+J6+J7),0)</f>
         <v/>
       </c>
       <c r="K10" s="12">
-        <f>IFERROR(Aannames!B45*(K5+K6+K7);0)</f>
+        <f>IFERROR(Aannames!B42*(K5+K6+K7),0)</f>
         <v/>
       </c>
       <c r="L10" s="12">
-        <f>IFERROR(Aannames!B45*(L5+L6+L7);0)</f>
+        <f>IFERROR(Aannames!B42*(L5+L6+L7),0)</f>
         <v/>
       </c>
       <c r="M10" s="12">
-        <f>IFERROR(Aannames!B45*(M5+M6+M7);0)</f>
+        <f>IFERROR(Aannames!B42*(M5+M6+M7),0)</f>
         <v/>
       </c>
       <c r="N10" s="12">
-        <f>IFERROR(Aannames!B45*(N5+N6+N7);0)</f>
+        <f>IFERROR(Aannames!B42*(N5+N6+N7),0)</f>
         <v/>
       </c>
       <c r="O10" s="12">
-        <f>IFERROR(Aannames!B45*(O5+O6+O7);0)</f>
+        <f>IFERROR(Aannames!B42*(O5+O6+O7),0)</f>
         <v/>
       </c>
       <c r="P10" s="12">
-        <f>IFERROR(Aannames!B45*(P5+P6+P7);0)</f>
+        <f>IFERROR(Aannames!B42*(P5+P6+P7),0)</f>
         <v/>
       </c>
       <c r="Q10" s="12">
-        <f>IFERROR(Aannames!B45*(Q5+Q6+Q7);0)</f>
+        <f>IFERROR(Aannames!B42*(Q5+Q6+Q7),0)</f>
         <v/>
       </c>
       <c r="R10" s="12">
-        <f>IFERROR(Aannames!B45*(R5+R6+R7);0)</f>
+        <f>IFERROR(Aannames!B42*(R5+R6+R7),0)</f>
         <v/>
       </c>
       <c r="S10" s="12">
-        <f>IFERROR(Aannames!B45*(S5+S6+S7);0)</f>
+        <f>IFERROR(Aannames!B42*(S5+S6+S7),0)</f>
         <v/>
       </c>
       <c r="T10" s="12">
-        <f>IFERROR(Aannames!B45*(T5+T6+T7);0)</f>
+        <f>IFERROR(Aannames!B42*(T5+T6+T7),0)</f>
         <v/>
       </c>
       <c r="U10" s="12">
-        <f>IFERROR(Aannames!B45*(U5+U6+U7);0)</f>
+        <f>IFERROR(Aannames!B42*(U5+U6+U7),0)</f>
         <v/>
       </c>
       <c r="V10" s="12">
-        <f>IFERROR(Aannames!B45*(V5+V6+V7);0)</f>
+        <f>IFERROR(Aannames!B42*(V5+V6+V7),0)</f>
         <v/>
       </c>
       <c r="W10" s="12">
-        <f>IFERROR(Aannames!B45*(W5+W6+W7);0)</f>
+        <f>IFERROR(Aannames!B42*(W5+W6+W7),0)</f>
         <v/>
       </c>
       <c r="X10" s="12">
-        <f>IFERROR(Aannames!B45*(X5+X6+X7);0)</f>
+        <f>IFERROR(Aannames!B42*(X5+X6+X7),0)</f>
         <v/>
       </c>
       <c r="Y10" s="12">
-        <f>IFERROR(Aannames!B45*(Y5+Y6+Y7);0)</f>
+        <f>IFERROR(Aannames!B42*(Y5+Y6+Y7),0)</f>
         <v/>
       </c>
       <c r="Z10" s="12">
-        <f>IFERROR(Aannames!B45*(Z5+Z6+Z7);0)</f>
+        <f>IFERROR(Aannames!B42*(Z5+Z6+Z7),0)</f>
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>IFERROR(Aannames!B45*(AA5+AA6+AA7);0)</f>
+        <f>IFERROR(Aannames!B42*(AA5+AA6+AA7),0)</f>
         <v/>
       </c>
       <c r="AB10" s="12">
-        <f>IFERROR(Aannames!B45*(AB5+AB6+AB7);0)</f>
+        <f>IFERROR(Aannames!B42*(AB5+AB6+AB7),0)</f>
         <v/>
       </c>
       <c r="AC10" s="12">
-        <f>IFERROR(Aannames!B45*(AC5+AC6+AC7);0)</f>
+        <f>IFERROR(Aannames!B42*(AC5+AC6+AC7),0)</f>
         <v/>
       </c>
       <c r="AD10" s="12">
-        <f>IFERROR(Aannames!B45*(AD5+AD6+AD7);0)</f>
+        <f>IFERROR(Aannames!B42*(AD5+AD6+AD7),0)</f>
         <v/>
       </c>
       <c r="AE10" s="12">
-        <f>IFERROR(Aannames!B45*(AE5+AE6+AE7);0)</f>
+        <f>IFERROR(Aannames!B42*(AE5+AE6+AE7),0)</f>
         <v/>
       </c>
       <c r="AF10" s="12">
-        <f>IFERROR(Aannames!B45*(AF5+AF6+AF7);0)</f>
+        <f>IFERROR(Aannames!B42*(AF5+AF6+AF7),0)</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IFERROR(Aannames!B45*(AG5+AG6+AG7);0)</f>
+        <f>IFERROR(Aannames!B42*(AG5+AG6+AG7),0)</f>
         <v/>
       </c>
       <c r="AH10" s="12">
-        <f>IFERROR(Aannames!B45*(AH5+AH6+AH7);0)</f>
+        <f>IFERROR(Aannames!B42*(AH5+AH6+AH7),0)</f>
         <v/>
       </c>
       <c r="AI10" s="12">
-        <f>IFERROR(Aannames!B45*(AI5+AI6+AI7);0)</f>
+        <f>IFERROR(Aannames!B42*(AI5+AI6+AI7),0)</f>
         <v/>
       </c>
       <c r="AJ10" s="12">
-        <f>IFERROR(Aannames!B45*(AJ5+AJ6+AJ7);0)</f>
+        <f>IFERROR(Aannames!B42*(AJ5+AJ6+AJ7),0)</f>
         <v/>
       </c>
       <c r="AK10" s="12">
-        <f>IFERROR(Aannames!B45*(AK5+AK6+AK7);0)</f>
+        <f>IFERROR(Aannames!B42*(AK5+AK6+AK7),0)</f>
         <v/>
       </c>
     </row>
@@ -7577,147 +7707,147 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>IFERROR('Verkoopprognose'!C166*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C166*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>IFERROR('Verkoopprognose'!C167*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C167*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>IFERROR('Verkoopprognose'!C168*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C168*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>IFERROR('Verkoopprognose'!C169*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C169*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>IFERROR('Verkoopprognose'!C170*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C170*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>IFERROR('Verkoopprognose'!C171*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C171*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="H11" s="12">
-        <f>IFERROR('Verkoopprognose'!C172*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C172*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="I11" s="12">
-        <f>IFERROR('Verkoopprognose'!C173*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C173*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="J11" s="12">
-        <f>IFERROR('Verkoopprognose'!C174*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C174*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="K11" s="12">
-        <f>IFERROR('Verkoopprognose'!C175*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C175*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="L11" s="12">
-        <f>IFERROR('Verkoopprognose'!C176*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C176*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="M11" s="12">
-        <f>IFERROR('Verkoopprognose'!C177*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C177*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="N11" s="12">
-        <f>IFERROR('Verkoopprognose'!C178*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C178*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="O11" s="12">
-        <f>IFERROR('Verkoopprognose'!C179*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C179*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="P11" s="12">
-        <f>IFERROR('Verkoopprognose'!C180*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C180*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="Q11" s="12">
-        <f>IFERROR('Verkoopprognose'!C181*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C181*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="R11" s="12">
-        <f>IFERROR('Verkoopprognose'!C182*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C182*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="S11" s="12">
-        <f>IFERROR('Verkoopprognose'!C183*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C183*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="T11" s="12">
-        <f>IFERROR('Verkoopprognose'!C184*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C184*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="U11" s="12">
-        <f>IFERROR('Verkoopprognose'!C185*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C185*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="V11" s="12">
-        <f>IFERROR('Verkoopprognose'!C186*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C186*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="W11" s="12">
-        <f>IFERROR('Verkoopprognose'!C187*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C187*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="X11" s="12">
-        <f>IFERROR('Verkoopprognose'!C188*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C188*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="Y11" s="12">
-        <f>IFERROR('Verkoopprognose'!C189*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C189*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="Z11" s="12">
-        <f>IFERROR('Verkoopprognose'!C190*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C190*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>IFERROR('Verkoopprognose'!C191*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C191*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AB11" s="12">
-        <f>IFERROR('Verkoopprognose'!C192*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C192*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AC11" s="12">
-        <f>IFERROR('Verkoopprognose'!C193*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C193*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AD11" s="12">
-        <f>IFERROR('Verkoopprognose'!C194*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C194*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AE11" s="12">
-        <f>IFERROR('Verkoopprognose'!C195*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C195*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AF11" s="12">
-        <f>IFERROR('Verkoopprognose'!C196*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C196*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IFERROR('Verkoopprognose'!C197*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C197*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AH11" s="12">
-        <f>IFERROR('Verkoopprognose'!C198*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C198*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AI11" s="12">
-        <f>IFERROR('Verkoopprognose'!C199*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C199*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AJ11" s="12">
-        <f>IFERROR('Verkoopprognose'!C200*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C200*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
       <c r="AK11" s="12">
-        <f>IFERROR('Verkoopprognose'!C201*Aannames!B30*Aannames!B31;0)</f>
+        <f>IFERROR('Verkoopprognose'!C201*Aannames!B27*Aannames!B28,0)</f>
         <v/>
       </c>
     </row>
@@ -7728,147 +7858,147 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>IFERROR('Verkoopprognose'!C206*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C206*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="C12" s="12">
-        <f>IFERROR('Verkoopprognose'!C207*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C207*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="D12" s="12">
-        <f>IFERROR('Verkoopprognose'!C208*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C208*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>IFERROR('Verkoopprognose'!C209*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C209*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="F12" s="12">
-        <f>IFERROR('Verkoopprognose'!C210*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C210*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="G12" s="12">
-        <f>IFERROR('Verkoopprognose'!C211*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C211*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="H12" s="12">
-        <f>IFERROR('Verkoopprognose'!C212*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C212*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="I12" s="12">
-        <f>IFERROR('Verkoopprognose'!C213*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C213*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="J12" s="12">
-        <f>IFERROR('Verkoopprognose'!C214*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C214*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="K12" s="12">
-        <f>IFERROR('Verkoopprognose'!C215*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C215*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="L12" s="12">
-        <f>IFERROR('Verkoopprognose'!C216*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C216*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="M12" s="12">
-        <f>IFERROR('Verkoopprognose'!C217*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C217*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="N12" s="12">
-        <f>IFERROR('Verkoopprognose'!C218*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C218*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="O12" s="12">
-        <f>IFERROR('Verkoopprognose'!C219*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C219*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="P12" s="12">
-        <f>IFERROR('Verkoopprognose'!C220*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C220*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="Q12" s="12">
-        <f>IFERROR('Verkoopprognose'!C221*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C221*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="R12" s="12">
-        <f>IFERROR('Verkoopprognose'!C222*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C222*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="S12" s="12">
-        <f>IFERROR('Verkoopprognose'!C223*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C223*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="T12" s="12">
-        <f>IFERROR('Verkoopprognose'!C224*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C224*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="U12" s="12">
-        <f>IFERROR('Verkoopprognose'!C225*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C225*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="V12" s="12">
-        <f>IFERROR('Verkoopprognose'!C226*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C226*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="W12" s="12">
-        <f>IFERROR('Verkoopprognose'!C227*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C227*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="X12" s="12">
-        <f>IFERROR('Verkoopprognose'!C228*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C228*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="Y12" s="12">
-        <f>IFERROR('Verkoopprognose'!C229*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C229*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="Z12" s="12">
-        <f>IFERROR('Verkoopprognose'!C230*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C230*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AA12" s="12">
-        <f>IFERROR('Verkoopprognose'!C231*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C231*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AB12" s="12">
-        <f>IFERROR('Verkoopprognose'!C232*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C232*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AC12" s="12">
-        <f>IFERROR('Verkoopprognose'!C233*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C233*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AD12" s="12">
-        <f>IFERROR('Verkoopprognose'!C234*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C234*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AE12" s="12">
-        <f>IFERROR('Verkoopprognose'!C235*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C235*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AF12" s="12">
-        <f>IFERROR('Verkoopprognose'!C236*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C236*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AG12" s="12">
-        <f>IFERROR('Verkoopprognose'!C237*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C237*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AH12" s="12">
-        <f>IFERROR('Verkoopprognose'!C238*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C238*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AI12" s="12">
-        <f>IFERROR('Verkoopprognose'!C239*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C239*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AJ12" s="12">
-        <f>IFERROR('Verkoopprognose'!C240*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C240*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
       <c r="AK12" s="12">
-        <f>IFERROR('Verkoopprognose'!C241*Aannames!B34*Aannames!B35;0)</f>
+        <f>IFERROR('Verkoopprognose'!C241*Aannames!B31*Aannames!B32,0)</f>
         <v/>
       </c>
     </row>
@@ -7879,147 +8009,147 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>IFERROR(SUM(B5:B12);0)</f>
+        <f>IFERROR(SUM(B5:B12),0)</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>IFERROR(SUM(C5:C12);0)</f>
+        <f>IFERROR(SUM(C5:C12),0)</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>IFERROR(SUM(D5:D12);0)</f>
+        <f>IFERROR(SUM(D5:D12),0)</f>
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>IFERROR(SUM(E5:E12);0)</f>
+        <f>IFERROR(SUM(E5:E12),0)</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>IFERROR(SUM(F5:F12);0)</f>
+        <f>IFERROR(SUM(F5:F12),0)</f>
         <v/>
       </c>
       <c r="G13" s="15">
-        <f>IFERROR(SUM(G5:G12);0)</f>
+        <f>IFERROR(SUM(G5:G12),0)</f>
         <v/>
       </c>
       <c r="H13" s="15">
-        <f>IFERROR(SUM(H5:H12);0)</f>
+        <f>IFERROR(SUM(H5:H12),0)</f>
         <v/>
       </c>
       <c r="I13" s="15">
-        <f>IFERROR(SUM(I5:I12);0)</f>
+        <f>IFERROR(SUM(I5:I12),0)</f>
         <v/>
       </c>
       <c r="J13" s="15">
-        <f>IFERROR(SUM(J5:J12);0)</f>
+        <f>IFERROR(SUM(J5:J12),0)</f>
         <v/>
       </c>
       <c r="K13" s="15">
-        <f>IFERROR(SUM(K5:K12);0)</f>
+        <f>IFERROR(SUM(K5:K12),0)</f>
         <v/>
       </c>
       <c r="L13" s="15">
-        <f>IFERROR(SUM(L5:L12);0)</f>
+        <f>IFERROR(SUM(L5:L12),0)</f>
         <v/>
       </c>
       <c r="M13" s="15">
-        <f>IFERROR(SUM(M5:M12);0)</f>
+        <f>IFERROR(SUM(M5:M12),0)</f>
         <v/>
       </c>
       <c r="N13" s="15">
-        <f>IFERROR(SUM(N5:N12);0)</f>
+        <f>IFERROR(SUM(N5:N12),0)</f>
         <v/>
       </c>
       <c r="O13" s="15">
-        <f>IFERROR(SUM(O5:O12);0)</f>
+        <f>IFERROR(SUM(O5:O12),0)</f>
         <v/>
       </c>
       <c r="P13" s="15">
-        <f>IFERROR(SUM(P5:P12);0)</f>
+        <f>IFERROR(SUM(P5:P12),0)</f>
         <v/>
       </c>
       <c r="Q13" s="15">
-        <f>IFERROR(SUM(Q5:Q12);0)</f>
+        <f>IFERROR(SUM(Q5:Q12),0)</f>
         <v/>
       </c>
       <c r="R13" s="15">
-        <f>IFERROR(SUM(R5:R12);0)</f>
+        <f>IFERROR(SUM(R5:R12),0)</f>
         <v/>
       </c>
       <c r="S13" s="15">
-        <f>IFERROR(SUM(S5:S12);0)</f>
+        <f>IFERROR(SUM(S5:S12),0)</f>
         <v/>
       </c>
       <c r="T13" s="15">
-        <f>IFERROR(SUM(T5:T12);0)</f>
+        <f>IFERROR(SUM(T5:T12),0)</f>
         <v/>
       </c>
       <c r="U13" s="15">
-        <f>IFERROR(SUM(U5:U12);0)</f>
+        <f>IFERROR(SUM(U5:U12),0)</f>
         <v/>
       </c>
       <c r="V13" s="15">
-        <f>IFERROR(SUM(V5:V12);0)</f>
+        <f>IFERROR(SUM(V5:V12),0)</f>
         <v/>
       </c>
       <c r="W13" s="15">
-        <f>IFERROR(SUM(W5:W12);0)</f>
+        <f>IFERROR(SUM(W5:W12),0)</f>
         <v/>
       </c>
       <c r="X13" s="15">
-        <f>IFERROR(SUM(X5:X12);0)</f>
+        <f>IFERROR(SUM(X5:X12),0)</f>
         <v/>
       </c>
       <c r="Y13" s="15">
-        <f>IFERROR(SUM(Y5:Y12);0)</f>
+        <f>IFERROR(SUM(Y5:Y12),0)</f>
         <v/>
       </c>
       <c r="Z13" s="15">
-        <f>IFERROR(SUM(Z5:Z12);0)</f>
+        <f>IFERROR(SUM(Z5:Z12),0)</f>
         <v/>
       </c>
       <c r="AA13" s="15">
-        <f>IFERROR(SUM(AA5:AA12);0)</f>
+        <f>IFERROR(SUM(AA5:AA12),0)</f>
         <v/>
       </c>
       <c r="AB13" s="15">
-        <f>IFERROR(SUM(AB5:AB12);0)</f>
+        <f>IFERROR(SUM(AB5:AB12),0)</f>
         <v/>
       </c>
       <c r="AC13" s="15">
-        <f>IFERROR(SUM(AC5:AC12);0)</f>
+        <f>IFERROR(SUM(AC5:AC12),0)</f>
         <v/>
       </c>
       <c r="AD13" s="15">
-        <f>IFERROR(SUM(AD5:AD12);0)</f>
+        <f>IFERROR(SUM(AD5:AD12),0)</f>
         <v/>
       </c>
       <c r="AE13" s="15">
-        <f>IFERROR(SUM(AE5:AE12);0)</f>
+        <f>IFERROR(SUM(AE5:AE12),0)</f>
         <v/>
       </c>
       <c r="AF13" s="15">
-        <f>IFERROR(SUM(AF5:AF12);0)</f>
+        <f>IFERROR(SUM(AF5:AF12),0)</f>
         <v/>
       </c>
       <c r="AG13" s="15">
-        <f>IFERROR(SUM(AG5:AG12);0)</f>
+        <f>IFERROR(SUM(AG5:AG12),0)</f>
         <v/>
       </c>
       <c r="AH13" s="15">
-        <f>IFERROR(SUM(AH5:AH12);0)</f>
+        <f>IFERROR(SUM(AH5:AH12),0)</f>
         <v/>
       </c>
       <c r="AI13" s="15">
-        <f>IFERROR(SUM(AI5:AI12);0)</f>
+        <f>IFERROR(SUM(AI5:AI12),0)</f>
         <v/>
       </c>
       <c r="AJ13" s="15">
-        <f>IFERROR(SUM(AJ5:AJ12);0)</f>
+        <f>IFERROR(SUM(AJ5:AJ12),0)</f>
         <v/>
       </c>
       <c r="AK13" s="15">
-        <f>IFERROR(SUM(AK5:AK12);0)</f>
+        <f>IFERROR(SUM(AK5:AK12),0)</f>
         <v/>
       </c>
     </row>
@@ -8074,147 +8204,147 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>IFERROR('Verkoopprognose'!C6*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C6*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR('Verkoopprognose'!C7*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C7*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>IFERROR('Verkoopprognose'!C8*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C8*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR('Verkoopprognose'!C9*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C9*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR('Verkoopprognose'!C10*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C10*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>IFERROR('Verkoopprognose'!C11*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C11*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>IFERROR('Verkoopprognose'!C12*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C12*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="I16" s="12">
-        <f>IFERROR('Verkoopprognose'!C13*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C13*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="J16" s="12">
-        <f>IFERROR('Verkoopprognose'!C14*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C14*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="K16" s="12">
-        <f>IFERROR('Verkoopprognose'!C15*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C15*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="L16" s="12">
-        <f>IFERROR('Verkoopprognose'!C16*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C16*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="M16" s="12">
-        <f>IFERROR('Verkoopprognose'!C17*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C17*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="N16" s="12">
-        <f>IFERROR('Verkoopprognose'!C18*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C18*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="O16" s="12">
-        <f>IFERROR('Verkoopprognose'!C19*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C19*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="P16" s="12">
-        <f>IFERROR('Verkoopprognose'!C20*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C20*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="Q16" s="12">
-        <f>IFERROR('Verkoopprognose'!C21*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C21*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="R16" s="12">
-        <f>IFERROR('Verkoopprognose'!C22*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C22*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="S16" s="12">
-        <f>IFERROR('Verkoopprognose'!C23*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C23*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="T16" s="12">
-        <f>IFERROR('Verkoopprognose'!C24*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C24*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="U16" s="12">
-        <f>IFERROR('Verkoopprognose'!C25*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C25*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="V16" s="12">
-        <f>IFERROR('Verkoopprognose'!C26*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C26*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="W16" s="12">
-        <f>IFERROR('Verkoopprognose'!C27*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C27*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="X16" s="12">
-        <f>IFERROR('Verkoopprognose'!C28*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C28*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="Y16" s="12">
-        <f>IFERROR('Verkoopprognose'!C29*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C29*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="Z16" s="12">
-        <f>IFERROR('Verkoopprognose'!C30*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C30*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AA16" s="12">
-        <f>IFERROR('Verkoopprognose'!C31*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C31*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AB16" s="12">
-        <f>IFERROR('Verkoopprognose'!C32*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C32*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AC16" s="12">
-        <f>IFERROR('Verkoopprognose'!C33*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C33*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AD16" s="12">
-        <f>IFERROR('Verkoopprognose'!C34*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C34*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AE16" s="12">
-        <f>IFERROR('Verkoopprognose'!C35*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C35*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AF16" s="12">
-        <f>IFERROR('Verkoopprognose'!C36*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C36*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AG16" s="12">
-        <f>IFERROR('Verkoopprognose'!C37*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C37*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AH16" s="12">
-        <f>IFERROR('Verkoopprognose'!C38*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C38*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AI16" s="12">
-        <f>IFERROR('Verkoopprognose'!C39*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C39*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AJ16" s="12">
-        <f>IFERROR('Verkoopprognose'!C40*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C40*Kosten!C6,0)</f>
         <v/>
       </c>
       <c r="AK16" s="12">
-        <f>IFERROR('Verkoopprognose'!C41*Aannames!B12;0)</f>
+        <f>IFERROR('Verkoopprognose'!C41*Kosten!C6,0)</f>
         <v/>
       </c>
     </row>
@@ -8225,147 +8355,147 @@
         </is>
       </c>
       <c r="B17" s="12">
-        <f>IFERROR('Verkoopprognose'!C46*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C46*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR('Verkoopprognose'!C47*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C47*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>IFERROR('Verkoopprognose'!C48*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C48*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IFERROR('Verkoopprognose'!C49*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C49*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>IFERROR('Verkoopprognose'!C50*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C50*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="G17" s="12">
-        <f>IFERROR('Verkoopprognose'!C51*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C51*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>IFERROR('Verkoopprognose'!C52*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C52*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="I17" s="12">
-        <f>IFERROR('Verkoopprognose'!C53*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C53*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="J17" s="12">
-        <f>IFERROR('Verkoopprognose'!C54*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C54*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="K17" s="12">
-        <f>IFERROR('Verkoopprognose'!C55*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C55*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="L17" s="12">
-        <f>IFERROR('Verkoopprognose'!C56*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C56*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="M17" s="12">
-        <f>IFERROR('Verkoopprognose'!C57*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C57*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="N17" s="12">
-        <f>IFERROR('Verkoopprognose'!C58*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C58*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="O17" s="12">
-        <f>IFERROR('Verkoopprognose'!C59*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C59*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="P17" s="12">
-        <f>IFERROR('Verkoopprognose'!C60*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C60*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="Q17" s="12">
-        <f>IFERROR('Verkoopprognose'!C61*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C61*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="R17" s="12">
-        <f>IFERROR('Verkoopprognose'!C62*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C62*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="S17" s="12">
-        <f>IFERROR('Verkoopprognose'!C63*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C63*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="T17" s="12">
-        <f>IFERROR('Verkoopprognose'!C64*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C64*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="U17" s="12">
-        <f>IFERROR('Verkoopprognose'!C65*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C65*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="V17" s="12">
-        <f>IFERROR('Verkoopprognose'!C66*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C66*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="W17" s="12">
-        <f>IFERROR('Verkoopprognose'!C67*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C67*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="X17" s="12">
-        <f>IFERROR('Verkoopprognose'!C68*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C68*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="Y17" s="12">
-        <f>IFERROR('Verkoopprognose'!C69*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C69*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="Z17" s="12">
-        <f>IFERROR('Verkoopprognose'!C70*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C70*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AA17" s="12">
-        <f>IFERROR('Verkoopprognose'!C71*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C71*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AB17" s="12">
-        <f>IFERROR('Verkoopprognose'!C72*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C72*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AC17" s="12">
-        <f>IFERROR('Verkoopprognose'!C73*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C73*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AD17" s="12">
-        <f>IFERROR('Verkoopprognose'!C74*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C74*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AE17" s="12">
-        <f>IFERROR('Verkoopprognose'!C75*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C75*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AF17" s="12">
-        <f>IFERROR('Verkoopprognose'!C76*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C76*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AG17" s="12">
-        <f>IFERROR('Verkoopprognose'!C77*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C77*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AH17" s="12">
-        <f>IFERROR('Verkoopprognose'!C78*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C78*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AI17" s="12">
-        <f>IFERROR('Verkoopprognose'!C79*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C79*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AJ17" s="12">
-        <f>IFERROR('Verkoopprognose'!C80*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C80*Kosten!C7,0)</f>
         <v/>
       </c>
       <c r="AK17" s="12">
-        <f>IFERROR('Verkoopprognose'!C81*Aannames!B16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C81*Kosten!C7,0)</f>
         <v/>
       </c>
     </row>
@@ -8376,147 +8506,147 @@
         </is>
       </c>
       <c r="B18" s="12">
-        <f>IFERROR('Verkoopprognose'!C86*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C86*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR('Verkoopprognose'!C87*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C87*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>IFERROR('Verkoopprognose'!C88*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C88*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IFERROR('Verkoopprognose'!C89*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C89*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>IFERROR('Verkoopprognose'!C90*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C90*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="G18" s="12">
-        <f>IFERROR('Verkoopprognose'!C91*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C91*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="H18" s="12">
-        <f>IFERROR('Verkoopprognose'!C92*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C92*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="I18" s="12">
-        <f>IFERROR('Verkoopprognose'!C93*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C93*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="J18" s="12">
-        <f>IFERROR('Verkoopprognose'!C94*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C94*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="K18" s="12">
-        <f>IFERROR('Verkoopprognose'!C95*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C95*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="L18" s="12">
-        <f>IFERROR('Verkoopprognose'!C96*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C96*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="M18" s="12">
-        <f>IFERROR('Verkoopprognose'!C97*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C97*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="N18" s="12">
-        <f>IFERROR('Verkoopprognose'!C98*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C98*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="O18" s="12">
-        <f>IFERROR('Verkoopprognose'!C99*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C99*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="P18" s="12">
-        <f>IFERROR('Verkoopprognose'!C100*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C100*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="Q18" s="12">
-        <f>IFERROR('Verkoopprognose'!C101*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C101*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="R18" s="12">
-        <f>IFERROR('Verkoopprognose'!C102*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C102*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="S18" s="12">
-        <f>IFERROR('Verkoopprognose'!C103*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C103*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="T18" s="12">
-        <f>IFERROR('Verkoopprognose'!C104*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C104*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="U18" s="12">
-        <f>IFERROR('Verkoopprognose'!C105*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C105*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="V18" s="12">
-        <f>IFERROR('Verkoopprognose'!C106*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C106*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="W18" s="12">
-        <f>IFERROR('Verkoopprognose'!C107*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C107*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="X18" s="12">
-        <f>IFERROR('Verkoopprognose'!C108*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C108*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="Y18" s="12">
-        <f>IFERROR('Verkoopprognose'!C109*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C109*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="Z18" s="12">
-        <f>IFERROR('Verkoopprognose'!C110*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C110*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AA18" s="12">
-        <f>IFERROR('Verkoopprognose'!C111*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C111*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AB18" s="12">
-        <f>IFERROR('Verkoopprognose'!C112*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C112*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AC18" s="12">
-        <f>IFERROR('Verkoopprognose'!C113*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C113*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AD18" s="12">
-        <f>IFERROR('Verkoopprognose'!C114*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C114*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AE18" s="12">
-        <f>IFERROR('Verkoopprognose'!C115*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C115*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AF18" s="12">
-        <f>IFERROR('Verkoopprognose'!C116*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C116*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AG18" s="12">
-        <f>IFERROR('Verkoopprognose'!C117*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C117*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AH18" s="12">
-        <f>IFERROR('Verkoopprognose'!C118*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C118*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AI18" s="12">
-        <f>IFERROR('Verkoopprognose'!C119*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C119*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AJ18" s="12">
-        <f>IFERROR('Verkoopprognose'!C120*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C120*Kosten!C8,0)</f>
         <v/>
       </c>
       <c r="AK18" s="12">
-        <f>IFERROR('Verkoopprognose'!C121*Aannames!B20;0)</f>
+        <f>IFERROR('Verkoopprognose'!C121*Kosten!C8,0)</f>
         <v/>
       </c>
     </row>
@@ -8527,147 +8657,147 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>IFERROR('Verkoopprognose'!C7*Kosten!C13+'Verkoopprognose'!C46*Kosten!C14+'Verkoopprognose'!C85*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C6*Kosten!C12+'Verkoopprognose'!C46*Kosten!C13+'Verkoopprognose'!C86*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="C19" s="12">
-        <f>IFERROR('Verkoopprognose'!C8*Kosten!C13+'Verkoopprognose'!C47*Kosten!C14+'Verkoopprognose'!C86*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C7*Kosten!C12+'Verkoopprognose'!C47*Kosten!C13+'Verkoopprognose'!C87*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="D19" s="12">
-        <f>IFERROR('Verkoopprognose'!C9*Kosten!C13+'Verkoopprognose'!C48*Kosten!C14+'Verkoopprognose'!C87*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C8*Kosten!C12+'Verkoopprognose'!C48*Kosten!C13+'Verkoopprognose'!C88*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>IFERROR('Verkoopprognose'!C10*Kosten!C13+'Verkoopprognose'!C49*Kosten!C14+'Verkoopprognose'!C88*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C9*Kosten!C12+'Verkoopprognose'!C49*Kosten!C13+'Verkoopprognose'!C89*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>IFERROR('Verkoopprognose'!C11*Kosten!C13+'Verkoopprognose'!C50*Kosten!C14+'Verkoopprognose'!C89*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C10*Kosten!C12+'Verkoopprognose'!C50*Kosten!C13+'Verkoopprognose'!C90*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="G19" s="12">
-        <f>IFERROR('Verkoopprognose'!C12*Kosten!C13+'Verkoopprognose'!C51*Kosten!C14+'Verkoopprognose'!C90*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C11*Kosten!C12+'Verkoopprognose'!C51*Kosten!C13+'Verkoopprognose'!C91*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="H19" s="12">
-        <f>IFERROR('Verkoopprognose'!C13*Kosten!C13+'Verkoopprognose'!C52*Kosten!C14+'Verkoopprognose'!C91*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C12*Kosten!C12+'Verkoopprognose'!C52*Kosten!C13+'Verkoopprognose'!C92*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="I19" s="12">
-        <f>IFERROR('Verkoopprognose'!C14*Kosten!C13+'Verkoopprognose'!C53*Kosten!C14+'Verkoopprognose'!C92*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C13*Kosten!C12+'Verkoopprognose'!C53*Kosten!C13+'Verkoopprognose'!C93*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="J19" s="12">
-        <f>IFERROR('Verkoopprognose'!C15*Kosten!C13+'Verkoopprognose'!C54*Kosten!C14+'Verkoopprognose'!C93*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C14*Kosten!C12+'Verkoopprognose'!C54*Kosten!C13+'Verkoopprognose'!C94*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="K19" s="12">
-        <f>IFERROR('Verkoopprognose'!C16*Kosten!C13+'Verkoopprognose'!C55*Kosten!C14+'Verkoopprognose'!C94*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C15*Kosten!C12+'Verkoopprognose'!C55*Kosten!C13+'Verkoopprognose'!C95*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="L19" s="12">
-        <f>IFERROR('Verkoopprognose'!C17*Kosten!C13+'Verkoopprognose'!C56*Kosten!C14+'Verkoopprognose'!C95*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C16*Kosten!C12+'Verkoopprognose'!C56*Kosten!C13+'Verkoopprognose'!C96*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="M19" s="12">
-        <f>IFERROR('Verkoopprognose'!C18*Kosten!C13+'Verkoopprognose'!C57*Kosten!C14+'Verkoopprognose'!C96*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C17*Kosten!C12+'Verkoopprognose'!C57*Kosten!C13+'Verkoopprognose'!C97*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="N19" s="12">
-        <f>IFERROR('Verkoopprognose'!C19*Kosten!C13+'Verkoopprognose'!C58*Kosten!C14+'Verkoopprognose'!C97*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C18*Kosten!C12+'Verkoopprognose'!C58*Kosten!C13+'Verkoopprognose'!C98*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="O19" s="12">
-        <f>IFERROR('Verkoopprognose'!C20*Kosten!C13+'Verkoopprognose'!C59*Kosten!C14+'Verkoopprognose'!C98*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C19*Kosten!C12+'Verkoopprognose'!C59*Kosten!C13+'Verkoopprognose'!C99*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="P19" s="12">
-        <f>IFERROR('Verkoopprognose'!C21*Kosten!C13+'Verkoopprognose'!C60*Kosten!C14+'Verkoopprognose'!C99*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C20*Kosten!C12+'Verkoopprognose'!C60*Kosten!C13+'Verkoopprognose'!C100*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="Q19" s="12">
-        <f>IFERROR('Verkoopprognose'!C22*Kosten!C13+'Verkoopprognose'!C61*Kosten!C14+'Verkoopprognose'!C100*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C21*Kosten!C12+'Verkoopprognose'!C61*Kosten!C13+'Verkoopprognose'!C101*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="R19" s="12">
-        <f>IFERROR('Verkoopprognose'!C23*Kosten!C13+'Verkoopprognose'!C62*Kosten!C14+'Verkoopprognose'!C101*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C22*Kosten!C12+'Verkoopprognose'!C62*Kosten!C13+'Verkoopprognose'!C102*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="S19" s="12">
-        <f>IFERROR('Verkoopprognose'!C24*Kosten!C13+'Verkoopprognose'!C63*Kosten!C14+'Verkoopprognose'!C102*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C23*Kosten!C12+'Verkoopprognose'!C63*Kosten!C13+'Verkoopprognose'!C103*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="T19" s="12">
-        <f>IFERROR('Verkoopprognose'!C25*Kosten!C13+'Verkoopprognose'!C64*Kosten!C14+'Verkoopprognose'!C103*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C24*Kosten!C12+'Verkoopprognose'!C64*Kosten!C13+'Verkoopprognose'!C104*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="U19" s="12">
-        <f>IFERROR('Verkoopprognose'!C26*Kosten!C13+'Verkoopprognose'!C65*Kosten!C14+'Verkoopprognose'!C104*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C25*Kosten!C12+'Verkoopprognose'!C65*Kosten!C13+'Verkoopprognose'!C105*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="V19" s="12">
-        <f>IFERROR('Verkoopprognose'!C27*Kosten!C13+'Verkoopprognose'!C66*Kosten!C14+'Verkoopprognose'!C105*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C26*Kosten!C12+'Verkoopprognose'!C66*Kosten!C13+'Verkoopprognose'!C106*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="W19" s="12">
-        <f>IFERROR('Verkoopprognose'!C28*Kosten!C13+'Verkoopprognose'!C67*Kosten!C14+'Verkoopprognose'!C106*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C27*Kosten!C12+'Verkoopprognose'!C67*Kosten!C13+'Verkoopprognose'!C107*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="X19" s="12">
-        <f>IFERROR('Verkoopprognose'!C29*Kosten!C13+'Verkoopprognose'!C68*Kosten!C14+'Verkoopprognose'!C107*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C28*Kosten!C12+'Verkoopprognose'!C68*Kosten!C13+'Verkoopprognose'!C108*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="Y19" s="12">
-        <f>IFERROR('Verkoopprognose'!C30*Kosten!C13+'Verkoopprognose'!C69*Kosten!C14+'Verkoopprognose'!C108*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C29*Kosten!C12+'Verkoopprognose'!C69*Kosten!C13+'Verkoopprognose'!C109*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="Z19" s="12">
-        <f>IFERROR('Verkoopprognose'!C31*Kosten!C13+'Verkoopprognose'!C70*Kosten!C14+'Verkoopprognose'!C109*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C30*Kosten!C12+'Verkoopprognose'!C70*Kosten!C13+'Verkoopprognose'!C110*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AA19" s="12">
-        <f>IFERROR('Verkoopprognose'!C32*Kosten!C13+'Verkoopprognose'!C71*Kosten!C14+'Verkoopprognose'!C110*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C31*Kosten!C12+'Verkoopprognose'!C71*Kosten!C13+'Verkoopprognose'!C111*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AB19" s="12">
-        <f>IFERROR('Verkoopprognose'!C33*Kosten!C13+'Verkoopprognose'!C72*Kosten!C14+'Verkoopprognose'!C111*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C32*Kosten!C12+'Verkoopprognose'!C72*Kosten!C13+'Verkoopprognose'!C112*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AC19" s="12">
-        <f>IFERROR('Verkoopprognose'!C34*Kosten!C13+'Verkoopprognose'!C73*Kosten!C14+'Verkoopprognose'!C112*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C33*Kosten!C12+'Verkoopprognose'!C73*Kosten!C13+'Verkoopprognose'!C113*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AD19" s="12">
-        <f>IFERROR('Verkoopprognose'!C35*Kosten!C13+'Verkoopprognose'!C74*Kosten!C14+'Verkoopprognose'!C113*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C34*Kosten!C12+'Verkoopprognose'!C74*Kosten!C13+'Verkoopprognose'!C114*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AE19" s="12">
-        <f>IFERROR('Verkoopprognose'!C36*Kosten!C13+'Verkoopprognose'!C75*Kosten!C14+'Verkoopprognose'!C114*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C35*Kosten!C12+'Verkoopprognose'!C75*Kosten!C13+'Verkoopprognose'!C115*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AF19" s="12">
-        <f>IFERROR('Verkoopprognose'!C37*Kosten!C13+'Verkoopprognose'!C76*Kosten!C14+'Verkoopprognose'!C115*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C36*Kosten!C12+'Verkoopprognose'!C76*Kosten!C13+'Verkoopprognose'!C116*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AG19" s="12">
-        <f>IFERROR('Verkoopprognose'!C38*Kosten!C13+'Verkoopprognose'!C77*Kosten!C14+'Verkoopprognose'!C116*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C37*Kosten!C12+'Verkoopprognose'!C77*Kosten!C13+'Verkoopprognose'!C117*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AH19" s="12">
-        <f>IFERROR('Verkoopprognose'!C39*Kosten!C13+'Verkoopprognose'!C78*Kosten!C14+'Verkoopprognose'!C117*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C38*Kosten!C12+'Verkoopprognose'!C78*Kosten!C13+'Verkoopprognose'!C118*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AI19" s="12">
-        <f>IFERROR('Verkoopprognose'!C40*Kosten!C13+'Verkoopprognose'!C79*Kosten!C14+'Verkoopprognose'!C118*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C39*Kosten!C12+'Verkoopprognose'!C79*Kosten!C13+'Verkoopprognose'!C119*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AJ19" s="12">
-        <f>IFERROR('Verkoopprognose'!C41*Kosten!C13+'Verkoopprognose'!C80*Kosten!C14+'Verkoopprognose'!C119*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C40*Kosten!C12+'Verkoopprognose'!C80*Kosten!C13+'Verkoopprognose'!C120*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
       <c r="AK19" s="12">
-        <f>IFERROR('Verkoopprognose'!C42*Kosten!C13+'Verkoopprognose'!C81*Kosten!C14+'Verkoopprognose'!C120*Kosten!C15+Kosten!C16;0)</f>
+        <f>IFERROR('Verkoopprognose'!C41*Kosten!C12+'Verkoopprognose'!C81*Kosten!C13+'Verkoopprognose'!C121*Kosten!C14+Kosten!C15,0)</f>
         <v/>
       </c>
     </row>
@@ -8677,148 +8807,148 @@
           <t>Personeel</t>
         </is>
       </c>
-      <c r="B20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="C20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="E20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="F20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="H20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="K20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="L20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="27">
-        <f>IFERROR(Kosten!C21*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="N20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="O20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="P20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="R20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="S20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="T20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="U20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="V20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="W20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="X20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="27">
-        <f>IFERROR(Kosten!C22*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="Z20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AA20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AB20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AC20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AD20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AE20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AF20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AG20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AH20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AI20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
-        <v/>
-      </c>
-      <c r="AK20" s="27">
-        <f>IFERROR(Kosten!C23*(1+Kosten!C24)+Kosten!C25;0)</f>
+      <c r="B20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="I20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="L20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="12">
+        <f>IFERROR(Kosten!C19*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="N20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="O20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="P20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="R20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="S20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="T20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="U20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="V20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="W20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="X20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="12">
+        <f>IFERROR(Kosten!C20*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AC20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AI20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
+        <v/>
+      </c>
+      <c r="AK20" s="12">
+        <f>IFERROR(Kosten!C21*(1+Kosten!C22)+Kosten!C23,0)</f>
         <v/>
       </c>
     </row>
@@ -8828,148 +8958,148 @@
           <t>Marketing en sales</t>
         </is>
       </c>
-      <c r="B21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*B13;0)</f>
-        <v/>
-      </c>
-      <c r="C21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*C13;0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*D13;0)</f>
-        <v/>
-      </c>
-      <c r="E21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*E13;0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*F13;0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*G13;0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*H13;0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*I13;0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*J13;0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*K13;0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*L13;0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*M13;0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*N13;0)</f>
-        <v/>
-      </c>
-      <c r="O21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*O13;0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*P13;0)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*Q13;0)</f>
-        <v/>
-      </c>
-      <c r="R21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*R13;0)</f>
-        <v/>
-      </c>
-      <c r="S21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*S13;0)</f>
-        <v/>
-      </c>
-      <c r="T21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*T13;0)</f>
-        <v/>
-      </c>
-      <c r="U21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*U13;0)</f>
-        <v/>
-      </c>
-      <c r="V21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*V13;0)</f>
-        <v/>
-      </c>
-      <c r="W21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*W13;0)</f>
-        <v/>
-      </c>
-      <c r="X21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*X13;0)</f>
-        <v/>
-      </c>
-      <c r="Y21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*Y13;0)</f>
-        <v/>
-      </c>
-      <c r="Z21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*Z13;0)</f>
-        <v/>
-      </c>
-      <c r="AA21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AA13;0)</f>
-        <v/>
-      </c>
-      <c r="AB21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AB13;0)</f>
-        <v/>
-      </c>
-      <c r="AC21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AC13;0)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AD13;0)</f>
-        <v/>
-      </c>
-      <c r="AE21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AE13;0)</f>
-        <v/>
-      </c>
-      <c r="AF21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AF13;0)</f>
-        <v/>
-      </c>
-      <c r="AG21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AG13;0)</f>
-        <v/>
-      </c>
-      <c r="AH21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AH13;0)</f>
-        <v/>
-      </c>
-      <c r="AI21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AI13;0)</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AJ13;0)</f>
-        <v/>
-      </c>
-      <c r="AK21" s="27">
-        <f>IFERROR(Kosten!C30+Kosten!C31+Kosten!C32+Kosten!C34+Kosten!C33*AK13;0)</f>
+      <c r="B21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*B13,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*C13,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*D13,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*E13,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*F13,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*G13,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*H13,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*I13,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*J13,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*K13,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*L13,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*M13,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*N13,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*O13,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*P13,0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*Q13,0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*R13,0)</f>
+        <v/>
+      </c>
+      <c r="S21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*S13,0)</f>
+        <v/>
+      </c>
+      <c r="T21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*T13,0)</f>
+        <v/>
+      </c>
+      <c r="U21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*U13,0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*V13,0)</f>
+        <v/>
+      </c>
+      <c r="W21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*W13,0)</f>
+        <v/>
+      </c>
+      <c r="X21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*X13,0)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*Y13,0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*Z13,0)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AA13,0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AB13,0)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AC13,0)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AD13,0)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AE13,0)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AF13,0)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AG13,0)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AH13,0)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AI13,0)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AJ13,0)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="12">
+        <f>IFERROR(Kosten!C27+Kosten!C28+Kosten!C29+Kosten!C31+Kosten!C30*AK13,0)</f>
         <v/>
       </c>
     </row>
@@ -8979,148 +9109,148 @@
           <t>Kantoor en operations</t>
         </is>
       </c>
-      <c r="B22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="C22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="D22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="E22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="F22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="H22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="K22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="N22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="O22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="P22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="R22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="S22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="T22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="U22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="V22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="W22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="X22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="Y22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="Z22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AA22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AB22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AC22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AE22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AF22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AG22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AH22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AI22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
-        <v/>
-      </c>
-      <c r="AK22" s="27">
-        <f>IFERROR(Kosten!C38+Kosten!C39+Kosten!C40+Kosten!C41;0)</f>
+      <c r="B22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="O22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="P22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="R22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="S22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="T22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="U22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="V22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="W22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="X22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AB22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AC22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AG22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
+        <v/>
+      </c>
+      <c r="AK22" s="12">
+        <f>IFERROR(Kosten!C35+Kosten!C36+Kosten!C37+Kosten!C38,0)</f>
         <v/>
       </c>
     </row>
@@ -9130,148 +9260,148 @@
           <t>Software, tools en IT</t>
         </is>
       </c>
-      <c r="B23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="C23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="D23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="E23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="F23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="H23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="K23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="L23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="N23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="O23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="P23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="R23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="S23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="T23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="U23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="V23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="W23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="X23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="Y23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="Z23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AA23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AB23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AC23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AE23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AF23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AG23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AH23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AI23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
-        <v/>
-      </c>
-      <c r="AK23" s="27">
-        <f>IFERROR(Kosten!C45+Kosten!C46+Kosten!C47+Kosten!C48;0)</f>
+      <c r="B23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="O23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="R23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="S23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="T23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="U23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="V23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="W23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="X23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AB23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AC23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AE23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AF23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AG23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AH23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AI23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
+        <v/>
+      </c>
+      <c r="AK23" s="12">
+        <f>IFERROR(Kosten!C42+Kosten!C43+Kosten!C44+Kosten!C45,0)</f>
         <v/>
       </c>
     </row>
@@ -9281,148 +9411,148 @@
           <t>Verzekeringen en juridisch</t>
         </is>
       </c>
-      <c r="B24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="C24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="E24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="F24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="H24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="K24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="L24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="M24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="N24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="O24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="P24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="R24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="S24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="T24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="U24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="V24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="W24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="X24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="Y24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="Z24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AA24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AB24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AC24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AD24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AE24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AF24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AG24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AH24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AI24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
-        <v/>
-      </c>
-      <c r="AK24" s="27">
-        <f>IFERROR(Kosten!C52+Kosten!C53+Kosten!C54+Kosten!C55;0)</f>
+      <c r="B24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="L24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="N24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="O24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="R24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="S24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="T24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="U24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="V24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="W24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="X24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AE24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AF24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AG24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AH24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AI24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
+        <v/>
+      </c>
+      <c r="AK24" s="12">
+        <f>IFERROR(Kosten!C49+Kosten!C50+Kosten!C51+Kosten!C52,0)</f>
         <v/>
       </c>
     </row>
@@ -9433,147 +9563,147 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(B5+B6+B7)+Kosten!C71*SUM(B16:B24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(B5+B6+B7)+Kosten!C65*SUM(B16:B24),0)</f>
         <v/>
       </c>
       <c r="C25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(C5+C6+C7)+Kosten!C71*SUM(C16:C24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(C5+C6+C7)+Kosten!C65*SUM(C16:C24),0)</f>
         <v/>
       </c>
       <c r="D25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(D5+D6+D7)+Kosten!C71*SUM(D16:D24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(D5+D6+D7)+Kosten!C65*SUM(D16:D24),0)</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(E5+E6+E7)+Kosten!C71*SUM(E16:E24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(E5+E6+E7)+Kosten!C65*SUM(E16:E24),0)</f>
         <v/>
       </c>
       <c r="F25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(F5+F6+F7)+Kosten!C71*SUM(F16:F24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(F5+F6+F7)+Kosten!C65*SUM(F16:F24),0)</f>
         <v/>
       </c>
       <c r="G25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(G5+G6+G7)+Kosten!C71*SUM(G16:G24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(G5+G6+G7)+Kosten!C65*SUM(G16:G24),0)</f>
         <v/>
       </c>
       <c r="H25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(H5+H6+H7)+Kosten!C71*SUM(H16:H24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(H5+H6+H7)+Kosten!C65*SUM(H16:H24),0)</f>
         <v/>
       </c>
       <c r="I25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(I5+I6+I7)+Kosten!C71*SUM(I16:I24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(I5+I6+I7)+Kosten!C65*SUM(I16:I24),0)</f>
         <v/>
       </c>
       <c r="J25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(J5+J6+J7)+Kosten!C71*SUM(J16:J24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(J5+J6+J7)+Kosten!C65*SUM(J16:J24),0)</f>
         <v/>
       </c>
       <c r="K25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(K5+K6+K7)+Kosten!C71*SUM(K16:K24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(K5+K6+K7)+Kosten!C65*SUM(K16:K24),0)</f>
         <v/>
       </c>
       <c r="L25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(L5+L6+L7)+Kosten!C71*SUM(L16:L24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(L5+L6+L7)+Kosten!C65*SUM(L16:L24),0)</f>
         <v/>
       </c>
       <c r="M25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(M5+M6+M7)+Kosten!C71*SUM(M16:M24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(M5+M6+M7)+Kosten!C65*SUM(M16:M24),0)</f>
         <v/>
       </c>
       <c r="N25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(N5+N6+N7)+Kosten!C71*SUM(N16:N24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(N5+N6+N7)+Kosten!C65*SUM(N16:N24),0)</f>
         <v/>
       </c>
       <c r="O25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(O5+O6+O7)+Kosten!C71*SUM(O16:O24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(O5+O6+O7)+Kosten!C65*SUM(O16:O24),0)</f>
         <v/>
       </c>
       <c r="P25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(P5+P6+P7)+Kosten!C71*SUM(P16:P24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(P5+P6+P7)+Kosten!C65*SUM(P16:P24),0)</f>
         <v/>
       </c>
       <c r="Q25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(Q5+Q6+Q7)+Kosten!C71*SUM(Q16:Q24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(Q5+Q6+Q7)+Kosten!C65*SUM(Q16:Q24),0)</f>
         <v/>
       </c>
       <c r="R25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(R5+R6+R7)+Kosten!C71*SUM(R16:R24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(R5+R6+R7)+Kosten!C65*SUM(R16:R24),0)</f>
         <v/>
       </c>
       <c r="S25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(S5+S6+S7)+Kosten!C71*SUM(S16:S24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(S5+S6+S7)+Kosten!C65*SUM(S16:S24),0)</f>
         <v/>
       </c>
       <c r="T25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(T5+T6+T7)+Kosten!C71*SUM(T16:T24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(T5+T6+T7)+Kosten!C65*SUM(T16:T24),0)</f>
         <v/>
       </c>
       <c r="U25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(U5+U6+U7)+Kosten!C71*SUM(U16:U24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(U5+U6+U7)+Kosten!C65*SUM(U16:U24),0)</f>
         <v/>
       </c>
       <c r="V25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(V5+V6+V7)+Kosten!C71*SUM(V16:V24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(V5+V6+V7)+Kosten!C65*SUM(V16:V24),0)</f>
         <v/>
       </c>
       <c r="W25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(W5+W6+W7)+Kosten!C71*SUM(W16:W24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(W5+W6+W7)+Kosten!C65*SUM(W16:W24),0)</f>
         <v/>
       </c>
       <c r="X25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(X5+X6+X7)+Kosten!C71*SUM(X16:X24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(X5+X6+X7)+Kosten!C65*SUM(X16:X24),0)</f>
         <v/>
       </c>
       <c r="Y25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(Y5+Y6+Y7)+Kosten!C71*SUM(Y16:Y24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(Y5+Y6+Y7)+Kosten!C65*SUM(Y16:Y24),0)</f>
         <v/>
       </c>
       <c r="Z25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(Z5+Z6+Z7)+Kosten!C71*SUM(Z16:Z24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(Z5+Z6+Z7)+Kosten!C65*SUM(Z16:Z24),0)</f>
         <v/>
       </c>
       <c r="AA25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AA5+AA6+AA7)+Kosten!C71*SUM(AA16:AA24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AA5+AA6+AA7)+Kosten!C65*SUM(AA16:AA24),0)</f>
         <v/>
       </c>
       <c r="AB25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AB5+AB6+AB7)+Kosten!C71*SUM(AB16:AB24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AB5+AB6+AB7)+Kosten!C65*SUM(AB16:AB24),0)</f>
         <v/>
       </c>
       <c r="AC25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AC5+AC6+AC7)+Kosten!C71*SUM(AC16:AC24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AC5+AC6+AC7)+Kosten!C65*SUM(AC16:AC24),0)</f>
         <v/>
       </c>
       <c r="AD25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AD5+AD6+AD7)+Kosten!C71*SUM(AD16:AD24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AD5+AD6+AD7)+Kosten!C65*SUM(AD16:AD24),0)</f>
         <v/>
       </c>
       <c r="AE25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AE5+AE6+AE7)+Kosten!C71*SUM(AE16:AE24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AE5+AE6+AE7)+Kosten!C65*SUM(AE16:AE24),0)</f>
         <v/>
       </c>
       <c r="AF25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AF5+AF6+AF7)+Kosten!C71*SUM(AF16:AF24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AF5+AF6+AF7)+Kosten!C65*SUM(AF16:AF24),0)</f>
         <v/>
       </c>
       <c r="AG25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AG5+AG6+AG7)+Kosten!C71*SUM(AG16:AG24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AG5+AG6+AG7)+Kosten!C65*SUM(AG16:AG24),0)</f>
         <v/>
       </c>
       <c r="AH25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AH5+AH6+AH7)+Kosten!C71*SUM(AH16:AH24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AH5+AH6+AH7)+Kosten!C65*SUM(AH16:AH24),0)</f>
         <v/>
       </c>
       <c r="AI25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AI5+AI6+AI7)+Kosten!C71*SUM(AI16:AI24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AI5+AI6+AI7)+Kosten!C65*SUM(AI16:AI24),0)</f>
         <v/>
       </c>
       <c r="AJ25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AJ5+AJ6+AJ7)+Kosten!C71*SUM(AJ16:AJ24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AJ5+AJ6+AJ7)+Kosten!C65*SUM(AJ16:AJ24),0)</f>
         <v/>
       </c>
       <c r="AK25" s="12">
-        <f>IFERROR(Kosten!C59+Kosten!C68+Kosten!C69+Kosten!C70+(Kosten!C60+Kosten!C61)*(AK5+AK6+AK7)+Kosten!C71*SUM(AK16:AK24);0)</f>
+        <f>IFERROR(Kosten!C62+Kosten!C63+Kosten!C64+Kosten!C56+(Kosten!C57+Kosten!C58)*(AK5+AK6+AK7)+Kosten!C65*SUM(AK16:AK24),0)</f>
         <v/>
       </c>
     </row>
@@ -9584,147 +9714,147 @@
         </is>
       </c>
       <c r="B26" s="15">
-        <f>IFERROR(SUM(B16:B25);0)</f>
+        <f>IFERROR(SUM(B16:B25),0)</f>
         <v/>
       </c>
       <c r="C26" s="15">
-        <f>IFERROR(SUM(C16:C25);0)</f>
+        <f>IFERROR(SUM(C16:C25),0)</f>
         <v/>
       </c>
       <c r="D26" s="15">
-        <f>IFERROR(SUM(D16:D25);0)</f>
+        <f>IFERROR(SUM(D16:D25),0)</f>
         <v/>
       </c>
       <c r="E26" s="15">
-        <f>IFERROR(SUM(E16:E25);0)</f>
+        <f>IFERROR(SUM(E16:E25),0)</f>
         <v/>
       </c>
       <c r="F26" s="15">
-        <f>IFERROR(SUM(F16:F25);0)</f>
+        <f>IFERROR(SUM(F16:F25),0)</f>
         <v/>
       </c>
       <c r="G26" s="15">
-        <f>IFERROR(SUM(G16:G25);0)</f>
+        <f>IFERROR(SUM(G16:G25),0)</f>
         <v/>
       </c>
       <c r="H26" s="15">
-        <f>IFERROR(SUM(H16:H25);0)</f>
+        <f>IFERROR(SUM(H16:H25),0)</f>
         <v/>
       </c>
       <c r="I26" s="15">
-        <f>IFERROR(SUM(I16:I25);0)</f>
+        <f>IFERROR(SUM(I16:I25),0)</f>
         <v/>
       </c>
       <c r="J26" s="15">
-        <f>IFERROR(SUM(J16:J25);0)</f>
+        <f>IFERROR(SUM(J16:J25),0)</f>
         <v/>
       </c>
       <c r="K26" s="15">
-        <f>IFERROR(SUM(K16:K25);0)</f>
+        <f>IFERROR(SUM(K16:K25),0)</f>
         <v/>
       </c>
       <c r="L26" s="15">
-        <f>IFERROR(SUM(L16:L25);0)</f>
+        <f>IFERROR(SUM(L16:L25),0)</f>
         <v/>
       </c>
       <c r="M26" s="15">
-        <f>IFERROR(SUM(M16:M25);0)</f>
+        <f>IFERROR(SUM(M16:M25),0)</f>
         <v/>
       </c>
       <c r="N26" s="15">
-        <f>IFERROR(SUM(N16:N25);0)</f>
+        <f>IFERROR(SUM(N16:N25),0)</f>
         <v/>
       </c>
       <c r="O26" s="15">
-        <f>IFERROR(SUM(O16:O25);0)</f>
+        <f>IFERROR(SUM(O16:O25),0)</f>
         <v/>
       </c>
       <c r="P26" s="15">
-        <f>IFERROR(SUM(P16:P25);0)</f>
+        <f>IFERROR(SUM(P16:P25),0)</f>
         <v/>
       </c>
       <c r="Q26" s="15">
-        <f>IFERROR(SUM(Q16:Q25);0)</f>
+        <f>IFERROR(SUM(Q16:Q25),0)</f>
         <v/>
       </c>
       <c r="R26" s="15">
-        <f>IFERROR(SUM(R16:R25);0)</f>
+        <f>IFERROR(SUM(R16:R25),0)</f>
         <v/>
       </c>
       <c r="S26" s="15">
-        <f>IFERROR(SUM(S16:S25);0)</f>
+        <f>IFERROR(SUM(S16:S25),0)</f>
         <v/>
       </c>
       <c r="T26" s="15">
-        <f>IFERROR(SUM(T16:T25);0)</f>
+        <f>IFERROR(SUM(T16:T25),0)</f>
         <v/>
       </c>
       <c r="U26" s="15">
-        <f>IFERROR(SUM(U16:U25);0)</f>
+        <f>IFERROR(SUM(U16:U25),0)</f>
         <v/>
       </c>
       <c r="V26" s="15">
-        <f>IFERROR(SUM(V16:V25);0)</f>
+        <f>IFERROR(SUM(V16:V25),0)</f>
         <v/>
       </c>
       <c r="W26" s="15">
-        <f>IFERROR(SUM(W16:W25);0)</f>
+        <f>IFERROR(SUM(W16:W25),0)</f>
         <v/>
       </c>
       <c r="X26" s="15">
-        <f>IFERROR(SUM(X16:X25);0)</f>
+        <f>IFERROR(SUM(X16:X25),0)</f>
         <v/>
       </c>
       <c r="Y26" s="15">
-        <f>IFERROR(SUM(Y16:Y25);0)</f>
+        <f>IFERROR(SUM(Y16:Y25),0)</f>
         <v/>
       </c>
       <c r="Z26" s="15">
-        <f>IFERROR(SUM(Z16:Z25);0)</f>
+        <f>IFERROR(SUM(Z16:Z25),0)</f>
         <v/>
       </c>
       <c r="AA26" s="15">
-        <f>IFERROR(SUM(AA16:AA25);0)</f>
+        <f>IFERROR(SUM(AA16:AA25),0)</f>
         <v/>
       </c>
       <c r="AB26" s="15">
-        <f>IFERROR(SUM(AB16:AB25);0)</f>
+        <f>IFERROR(SUM(AB16:AB25),0)</f>
         <v/>
       </c>
       <c r="AC26" s="15">
-        <f>IFERROR(SUM(AC16:AC25);0)</f>
+        <f>IFERROR(SUM(AC16:AC25),0)</f>
         <v/>
       </c>
       <c r="AD26" s="15">
-        <f>IFERROR(SUM(AD16:AD25);0)</f>
+        <f>IFERROR(SUM(AD16:AD25),0)</f>
         <v/>
       </c>
       <c r="AE26" s="15">
-        <f>IFERROR(SUM(AE16:AE25);0)</f>
+        <f>IFERROR(SUM(AE16:AE25),0)</f>
         <v/>
       </c>
       <c r="AF26" s="15">
-        <f>IFERROR(SUM(AF16:AF25);0)</f>
+        <f>IFERROR(SUM(AF16:AF25),0)</f>
         <v/>
       </c>
       <c r="AG26" s="15">
-        <f>IFERROR(SUM(AG16:AG25);0)</f>
+        <f>IFERROR(SUM(AG16:AG25),0)</f>
         <v/>
       </c>
       <c r="AH26" s="15">
-        <f>IFERROR(SUM(AH16:AH25);0)</f>
+        <f>IFERROR(SUM(AH16:AH25),0)</f>
         <v/>
       </c>
       <c r="AI26" s="15">
-        <f>IFERROR(SUM(AI16:AI25);0)</f>
+        <f>IFERROR(SUM(AI16:AI25),0)</f>
         <v/>
       </c>
       <c r="AJ26" s="15">
-        <f>IFERROR(SUM(AJ16:AJ25);0)</f>
+        <f>IFERROR(SUM(AJ16:AJ25),0)</f>
         <v/>
       </c>
       <c r="AK26" s="15">
-        <f>IFERROR(SUM(AK16:AK25);0)</f>
+        <f>IFERROR(SUM(AK16:AK25),0)</f>
         <v/>
       </c>
     </row>
@@ -9736,147 +9866,147 @@
         </is>
       </c>
       <c r="B28" s="18">
-        <f>IFERROR(B13-B26;0)</f>
+        <f>IFERROR(B13-B26,0)</f>
         <v/>
       </c>
       <c r="C28" s="18">
-        <f>IFERROR(C13-C26;0)</f>
+        <f>IFERROR(C13-C26,0)</f>
         <v/>
       </c>
       <c r="D28" s="18">
-        <f>IFERROR(D13-D26;0)</f>
+        <f>IFERROR(D13-D26,0)</f>
         <v/>
       </c>
       <c r="E28" s="18">
-        <f>IFERROR(E13-E26;0)</f>
+        <f>IFERROR(E13-E26,0)</f>
         <v/>
       </c>
       <c r="F28" s="18">
-        <f>IFERROR(F13-F26;0)</f>
+        <f>IFERROR(F13-F26,0)</f>
         <v/>
       </c>
       <c r="G28" s="18">
-        <f>IFERROR(G13-G26;0)</f>
+        <f>IFERROR(G13-G26,0)</f>
         <v/>
       </c>
       <c r="H28" s="18">
-        <f>IFERROR(H13-H26;0)</f>
+        <f>IFERROR(H13-H26,0)</f>
         <v/>
       </c>
       <c r="I28" s="18">
-        <f>IFERROR(I13-I26;0)</f>
+        <f>IFERROR(I13-I26,0)</f>
         <v/>
       </c>
       <c r="J28" s="18">
-        <f>IFERROR(J13-J26;0)</f>
+        <f>IFERROR(J13-J26,0)</f>
         <v/>
       </c>
       <c r="K28" s="18">
-        <f>IFERROR(K13-K26;0)</f>
+        <f>IFERROR(K13-K26,0)</f>
         <v/>
       </c>
       <c r="L28" s="18">
-        <f>IFERROR(L13-L26;0)</f>
+        <f>IFERROR(L13-L26,0)</f>
         <v/>
       </c>
       <c r="M28" s="18">
-        <f>IFERROR(M13-M26;0)</f>
+        <f>IFERROR(M13-M26,0)</f>
         <v/>
       </c>
       <c r="N28" s="18">
-        <f>IFERROR(N13-N26;0)</f>
+        <f>IFERROR(N13-N26,0)</f>
         <v/>
       </c>
       <c r="O28" s="18">
-        <f>IFERROR(O13-O26;0)</f>
+        <f>IFERROR(O13-O26,0)</f>
         <v/>
       </c>
       <c r="P28" s="18">
-        <f>IFERROR(P13-P26;0)</f>
+        <f>IFERROR(P13-P26,0)</f>
         <v/>
       </c>
       <c r="Q28" s="18">
-        <f>IFERROR(Q13-Q26;0)</f>
+        <f>IFERROR(Q13-Q26,0)</f>
         <v/>
       </c>
       <c r="R28" s="18">
-        <f>IFERROR(R13-R26;0)</f>
+        <f>IFERROR(R13-R26,0)</f>
         <v/>
       </c>
       <c r="S28" s="18">
-        <f>IFERROR(S13-S26;0)</f>
+        <f>IFERROR(S13-S26,0)</f>
         <v/>
       </c>
       <c r="T28" s="18">
-        <f>IFERROR(T13-T26;0)</f>
+        <f>IFERROR(T13-T26,0)</f>
         <v/>
       </c>
       <c r="U28" s="18">
-        <f>IFERROR(U13-U26;0)</f>
+        <f>IFERROR(U13-U26,0)</f>
         <v/>
       </c>
       <c r="V28" s="18">
-        <f>IFERROR(V13-V26;0)</f>
+        <f>IFERROR(V13-V26,0)</f>
         <v/>
       </c>
       <c r="W28" s="18">
-        <f>IFERROR(W13-W26;0)</f>
+        <f>IFERROR(W13-W26,0)</f>
         <v/>
       </c>
       <c r="X28" s="18">
-        <f>IFERROR(X13-X26;0)</f>
+        <f>IFERROR(X13-X26,0)</f>
         <v/>
       </c>
       <c r="Y28" s="18">
-        <f>IFERROR(Y13-Y26;0)</f>
+        <f>IFERROR(Y13-Y26,0)</f>
         <v/>
       </c>
       <c r="Z28" s="18">
-        <f>IFERROR(Z13-Z26;0)</f>
+        <f>IFERROR(Z13-Z26,0)</f>
         <v/>
       </c>
       <c r="AA28" s="18">
-        <f>IFERROR(AA13-AA26;0)</f>
+        <f>IFERROR(AA13-AA26,0)</f>
         <v/>
       </c>
       <c r="AB28" s="18">
-        <f>IFERROR(AB13-AB26;0)</f>
+        <f>IFERROR(AB13-AB26,0)</f>
         <v/>
       </c>
       <c r="AC28" s="18">
-        <f>IFERROR(AC13-AC26;0)</f>
+        <f>IFERROR(AC13-AC26,0)</f>
         <v/>
       </c>
       <c r="AD28" s="18">
-        <f>IFERROR(AD13-AD26;0)</f>
+        <f>IFERROR(AD13-AD26,0)</f>
         <v/>
       </c>
       <c r="AE28" s="18">
-        <f>IFERROR(AE13-AE26;0)</f>
+        <f>IFERROR(AE13-AE26,0)</f>
         <v/>
       </c>
       <c r="AF28" s="18">
-        <f>IFERROR(AF13-AF26;0)</f>
+        <f>IFERROR(AF13-AF26,0)</f>
         <v/>
       </c>
       <c r="AG28" s="18">
-        <f>IFERROR(AG13-AG26;0)</f>
+        <f>IFERROR(AG13-AG26,0)</f>
         <v/>
       </c>
       <c r="AH28" s="18">
-        <f>IFERROR(AH13-AH26;0)</f>
+        <f>IFERROR(AH13-AH26,0)</f>
         <v/>
       </c>
       <c r="AI28" s="18">
-        <f>IFERROR(AI13-AI26;0)</f>
+        <f>IFERROR(AI13-AI26,0)</f>
         <v/>
       </c>
       <c r="AJ28" s="18">
-        <f>IFERROR(AJ13-AJ26;0)</f>
+        <f>IFERROR(AJ13-AJ26,0)</f>
         <v/>
       </c>
       <c r="AK28" s="18">
-        <f>IFERROR(AK13-AK26;0)</f>
+        <f>IFERROR(AK13-AK26,0)</f>
         <v/>
       </c>
     </row>
@@ -10182,6 +10312,8 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -10348,17 +10480,19 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Startkapitaal (EUR)</t>
         </is>
       </c>
-      <c r="B3" s="6">
-        <f>Aannames!B6</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B3" s="28">
+        <f>Aannames!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr"/>
       <c r="B5" s="10" t="inlineStr">
@@ -11944,6 +12078,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -13648,6 +13783,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
@@ -14144,6 +14280,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
@@ -14625,6 +14762,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
